--- a/data/excel/area-data.xlsx
+++ b/data/excel/area-data.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VScode\game-project\data\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\game-project\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9E07D3-278C-49F4-B884-E5E098C9A20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E3DCCA-2CDB-4A85-997A-1A5BF8F40EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1755" yWindow="1830" windowWidth="32085" windowHeight="20085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="870" yWindow="1095" windowWidth="25755" windowHeight="18915" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クエスト" sheetId="1" r:id="rId1"/>
-    <sheet name="エリア" sheetId="2" r:id="rId2"/>
-    <sheet name="イベント" sheetId="3" r:id="rId3"/>
+    <sheet name="イベント" sheetId="3" r:id="rId2"/>
+    <sheet name="エリア" sheetId="2" r:id="rId3"/>
     <sheet name="ダンジョン" sheetId="4" r:id="rId4"/>
     <sheet name="エネミー" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="rnn1U/JkVWRj5ItZ21T5UEH0ssWH9f0bbvlmVekus6c="/>
     </ext>
@@ -20523,4108 +20534,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="Sheet2">
-    <tabColor rgb="FFFBE4D5"/>
-  </sheetPr>
-  <dimension ref="A1:Q1008"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="4" max="5" width="4.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" customWidth="1"/>
-    <col min="11" max="11" width="29.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="29" width="9.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>444</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="L1" s="18" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" s="14" t="str">
-        <f>"宿部屋"&amp;".webp"</f>
-        <v>宿部屋.webp</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>438</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>439</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>441</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>442</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="6"/>
-      <c r="K12" s="7"/>
-    </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>486</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>436</v>
-      </c>
-      <c r="D13" s="18">
-        <v>258</v>
-      </c>
-      <c r="E13" s="18">
-        <v>137</v>
-      </c>
-      <c r="F13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="M13" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="B14" t="s">
-        <v>446</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D14" s="18">
-        <v>231</v>
-      </c>
-      <c r="E14" s="18">
-        <v>134</v>
-      </c>
-      <c r="F14" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="M14" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>413</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>436</v>
-      </c>
-      <c r="D15" s="18">
-        <v>264.5</v>
-      </c>
-      <c r="E15" s="18">
-        <v>163</v>
-      </c>
-      <c r="F15" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>414</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="B16" t="s">
-        <v>416</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="18">
-        <v>236</v>
-      </c>
-      <c r="E16" s="18">
-        <v>157</v>
-      </c>
-      <c r="F16" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="M16" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="B17" t="s">
-        <v>447</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="18">
-        <v>248</v>
-      </c>
-      <c r="E17" s="18">
-        <v>133</v>
-      </c>
-      <c r="F17" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="14" t="str">
-        <f t="shared" ref="G17:G23" si="0">A17&amp;".webp"</f>
-        <v>森農場.webp</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>502</v>
-      </c>
-      <c r="M17" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>495</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>畑.webp</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>507</v>
-      </c>
-      <c r="B19" t="s">
-        <v>448</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="18">
-        <v>251</v>
-      </c>
-      <c r="E19" s="18">
-        <v>142</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>水脈森.webp</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>488</v>
-      </c>
-      <c r="M19" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>480</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="18">
-        <v>253</v>
-      </c>
-      <c r="E20" s="18">
-        <v>155</v>
-      </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>獣の森.webp</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>509</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>獣の森・水辺.webp</v>
-      </c>
-      <c r="H21" s="18"/>
-      <c r="J21" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K21" s="18"/>
-      <c r="M21" s="6"/>
-    </row>
-    <row r="22" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>獣の森・森林.webp</v>
-      </c>
-      <c r="H22" s="18"/>
-      <c r="J22" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K22" s="18"/>
-      <c r="M22" s="6"/>
-    </row>
-    <row r="23" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>獣の森・沼地.webp</v>
-      </c>
-      <c r="H23" s="18"/>
-      <c r="J23" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K23" s="18"/>
-      <c r="M23" s="6"/>
-    </row>
-    <row r="24" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="18"/>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="18"/>
-      <c r="M25" s="6"/>
-    </row>
-    <row r="26" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="18"/>
-      <c r="M26" s="6"/>
-    </row>
-    <row r="27" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="B27" t="s">
-        <v>450</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D27" s="18">
-        <v>269</v>
-      </c>
-      <c r="E27" s="18">
-        <v>118</v>
-      </c>
-      <c r="F27" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14" t="str">
-        <f t="shared" ref="G27:G32" si="1">A27&amp;".webp"</f>
-        <v>負の跡地.webp</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>428</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K27" s="18" t="s">
-        <v>486</v>
-      </c>
-      <c r="M27" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>482</v>
-      </c>
-      <c r="B28" t="s">
-        <v>451</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D28" s="18">
-        <v>232</v>
-      </c>
-      <c r="E28" s="18">
-        <v>120</v>
-      </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>海沿いの森.webp</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K28" s="18" t="s">
-        <v>486</v>
-      </c>
-      <c r="M28" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
-        <v>487</v>
-      </c>
-      <c r="B29" t="s">
-        <v>456</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="D29" s="18">
-        <v>255</v>
-      </c>
-      <c r="E29" s="18">
-        <v>178</v>
-      </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>大鉱山.webp</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="M29" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="B30" t="s">
-        <v>452</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="D30" s="18">
-        <v>324</v>
-      </c>
-      <c r="E30" s="18">
-        <v>130</v>
-      </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>大森林.webp</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="M30" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="B31" t="s">
-        <v>453</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="D31" s="18">
-        <v>253</v>
-      </c>
-      <c r="E31" s="18">
-        <v>95</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>砂漠山.webp</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="M31" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="B32" t="s">
-        <v>454</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="D32" s="18">
-        <v>295</v>
-      </c>
-      <c r="E32" s="18">
-        <v>90</v>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>戦場後.webp</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="M32" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>433</v>
-      </c>
-      <c r="B33" t="s">
-        <v>433</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="18">
-        <v>264</v>
-      </c>
-      <c r="E33" s="18">
-        <v>66</v>
-      </c>
-      <c r="F33" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="M33" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="B34" t="s">
-        <v>455</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="D34" s="18">
-        <v>268</v>
-      </c>
-      <c r="E34" s="18">
-        <v>189</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K34" s="7"/>
-      <c r="M34" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>457</v>
-      </c>
-      <c r="B35" t="s">
-        <v>458</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="D35">
-        <v>283</v>
-      </c>
-      <c r="E35">
-        <v>207</v>
-      </c>
-      <c r="F35" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" s="7"/>
-      <c r="M35" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>459</v>
-      </c>
-      <c r="B36" t="s">
-        <v>460</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="D36">
-        <v>315.5</v>
-      </c>
-      <c r="E36">
-        <v>218</v>
-      </c>
-      <c r="F36" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" s="7"/>
-      <c r="M36" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>461</v>
-      </c>
-      <c r="B37" t="s">
-        <v>462</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="D37">
-        <v>341</v>
-      </c>
-      <c r="E37">
-        <v>207</v>
-      </c>
-      <c r="F37" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" s="7"/>
-      <c r="M37" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>463</v>
-      </c>
-      <c r="B38" t="s">
-        <v>464</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>476</v>
-      </c>
-      <c r="D38">
-        <v>341</v>
-      </c>
-      <c r="E38">
-        <v>225</v>
-      </c>
-      <c r="F38" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" s="7"/>
-      <c r="M38" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>465</v>
-      </c>
-      <c r="B39" t="s">
-        <v>465</v>
-      </c>
-      <c r="C39" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39">
-        <v>381</v>
-      </c>
-      <c r="E39">
-        <v>121</v>
-      </c>
-      <c r="F39" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" s="7"/>
-      <c r="M39" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>466</v>
-      </c>
-      <c r="B40" t="s">
-        <v>467</v>
-      </c>
-      <c r="C40" t="s">
-        <v>472</v>
-      </c>
-      <c r="D40">
-        <v>483</v>
-      </c>
-      <c r="E40">
-        <v>86</v>
-      </c>
-      <c r="F40" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" s="7"/>
-      <c r="M40" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>468</v>
-      </c>
-      <c r="B41" t="s">
-        <v>469</v>
-      </c>
-      <c r="C41" t="s">
-        <v>205</v>
-      </c>
-      <c r="D41">
-        <v>488</v>
-      </c>
-      <c r="E41">
-        <v>77</v>
-      </c>
-      <c r="F41" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" s="7"/>
-      <c r="M41" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>470</v>
-      </c>
-      <c r="B42" t="s">
-        <v>471</v>
-      </c>
-      <c r="C42" t="s">
-        <v>472</v>
-      </c>
-      <c r="D42">
-        <v>333</v>
-      </c>
-      <c r="E42">
-        <v>353</v>
-      </c>
-      <c r="F42" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" s="7"/>
-      <c r="M42" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>473</v>
-      </c>
-      <c r="B43" t="s">
-        <v>474</v>
-      </c>
-      <c r="C43" t="s">
-        <v>205</v>
-      </c>
-      <c r="D43">
-        <v>289</v>
-      </c>
-      <c r="E43">
-        <v>493</v>
-      </c>
-      <c r="F43" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" s="7"/>
-      <c r="M43" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="B44" t="s">
-        <v>475</v>
-      </c>
-      <c r="C44" t="s">
-        <v>472</v>
-      </c>
-      <c r="D44">
-        <v>222.5</v>
-      </c>
-      <c r="E44">
-        <v>352</v>
-      </c>
-      <c r="F44" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" s="7"/>
-      <c r="M44" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K45" s="7"/>
-    </row>
-    <row r="46" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K46" s="7"/>
-    </row>
-    <row r="47" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K47" s="7"/>
-    </row>
-    <row r="48" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K48" s="7"/>
-    </row>
-    <row r="49" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K49" s="7"/>
-    </row>
-    <row r="50" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K51" s="7"/>
-    </row>
-    <row r="52" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K52" s="7"/>
-    </row>
-    <row r="53" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K53" s="7"/>
-    </row>
-    <row r="54" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K54" s="7"/>
-    </row>
-    <row r="55" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K55" s="7"/>
-    </row>
-    <row r="56" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K56" s="7"/>
-    </row>
-    <row r="57" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K57" s="7"/>
-    </row>
-    <row r="58" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K58" s="7"/>
-    </row>
-    <row r="59" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K59" s="7"/>
-    </row>
-    <row r="60" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K60" s="7"/>
-    </row>
-    <row r="61" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K61" s="7"/>
-    </row>
-    <row r="62" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K62" s="7"/>
-    </row>
-    <row r="63" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K63" s="7"/>
-    </row>
-    <row r="64" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K64" s="7"/>
-    </row>
-    <row r="65" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K65" s="7"/>
-    </row>
-    <row r="66" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K66" s="7"/>
-    </row>
-    <row r="67" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K67" s="7"/>
-    </row>
-    <row r="68" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K68" s="7"/>
-    </row>
-    <row r="69" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K69" s="7"/>
-    </row>
-    <row r="70" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K70" s="7"/>
-    </row>
-    <row r="71" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K71" s="7"/>
-    </row>
-    <row r="72" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K72" s="7"/>
-    </row>
-    <row r="73" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K73" s="7"/>
-    </row>
-    <row r="74" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K74" s="7"/>
-    </row>
-    <row r="75" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K75" s="7"/>
-    </row>
-    <row r="76" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K76" s="7"/>
-    </row>
-    <row r="77" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K77" s="7"/>
-    </row>
-    <row r="78" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K78" s="7"/>
-    </row>
-    <row r="79" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K79" s="7"/>
-    </row>
-    <row r="80" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K80" s="7"/>
-    </row>
-    <row r="81" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K81" s="7"/>
-    </row>
-    <row r="82" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K82" s="7"/>
-    </row>
-    <row r="83" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K83" s="7"/>
-    </row>
-    <row r="84" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K84" s="7"/>
-    </row>
-    <row r="85" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K85" s="7"/>
-    </row>
-    <row r="86" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K86" s="7"/>
-    </row>
-    <row r="87" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K87" s="7"/>
-    </row>
-    <row r="88" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K88" s="7"/>
-    </row>
-    <row r="89" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K89" s="7"/>
-    </row>
-    <row r="90" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K90" s="7"/>
-    </row>
-    <row r="91" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K91" s="7"/>
-    </row>
-    <row r="92" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K92" s="7"/>
-    </row>
-    <row r="93" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K93" s="7"/>
-    </row>
-    <row r="94" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K94" s="7"/>
-    </row>
-    <row r="95" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K95" s="7"/>
-    </row>
-    <row r="96" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K96" s="7"/>
-    </row>
-    <row r="97" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K97" s="7"/>
-    </row>
-    <row r="98" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K98" s="7"/>
-    </row>
-    <row r="99" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K99" s="7"/>
-    </row>
-    <row r="100" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K100" s="7"/>
-    </row>
-    <row r="101" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K101" s="7"/>
-    </row>
-    <row r="102" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K102" s="7"/>
-    </row>
-    <row r="103" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K103" s="7"/>
-    </row>
-    <row r="104" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K104" s="7"/>
-    </row>
-    <row r="105" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K105" s="7"/>
-    </row>
-    <row r="106" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K106" s="7"/>
-    </row>
-    <row r="107" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K107" s="7"/>
-    </row>
-    <row r="108" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K108" s="7"/>
-    </row>
-    <row r="109" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K109" s="7"/>
-    </row>
-    <row r="110" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K110" s="7"/>
-    </row>
-    <row r="111" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K111" s="7"/>
-    </row>
-    <row r="112" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K112" s="7"/>
-    </row>
-    <row r="113" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K113" s="7"/>
-    </row>
-    <row r="114" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K114" s="7"/>
-    </row>
-    <row r="115" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K115" s="7"/>
-    </row>
-    <row r="116" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K116" s="7"/>
-    </row>
-    <row r="117" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K117" s="7"/>
-    </row>
-    <row r="118" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K118" s="7"/>
-    </row>
-    <row r="119" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K119" s="7"/>
-    </row>
-    <row r="120" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K120" s="7"/>
-    </row>
-    <row r="121" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K121" s="7"/>
-    </row>
-    <row r="122" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K122" s="7"/>
-    </row>
-    <row r="123" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K123" s="7"/>
-    </row>
-    <row r="124" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K124" s="7"/>
-    </row>
-    <row r="125" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K125" s="7"/>
-    </row>
-    <row r="126" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K126" s="7"/>
-    </row>
-    <row r="127" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K127" s="7"/>
-    </row>
-    <row r="128" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K128" s="7"/>
-    </row>
-    <row r="129" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K129" s="7"/>
-    </row>
-    <row r="130" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K130" s="7"/>
-    </row>
-    <row r="131" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K131" s="7"/>
-    </row>
-    <row r="132" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K132" s="7"/>
-    </row>
-    <row r="133" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K133" s="7"/>
-    </row>
-    <row r="134" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K134" s="7"/>
-    </row>
-    <row r="135" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K135" s="7"/>
-    </row>
-    <row r="136" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K136" s="7"/>
-    </row>
-    <row r="137" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K137" s="7"/>
-    </row>
-    <row r="138" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K138" s="7"/>
-    </row>
-    <row r="139" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K139" s="7"/>
-    </row>
-    <row r="140" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K140" s="7"/>
-    </row>
-    <row r="141" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K141" s="7"/>
-    </row>
-    <row r="142" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K142" s="7"/>
-    </row>
-    <row r="143" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K143" s="7"/>
-    </row>
-    <row r="144" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K144" s="7"/>
-    </row>
-    <row r="145" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K145" s="7"/>
-    </row>
-    <row r="146" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K146" s="7"/>
-    </row>
-    <row r="147" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K147" s="7"/>
-    </row>
-    <row r="148" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K148" s="7"/>
-    </row>
-    <row r="149" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K149" s="7"/>
-    </row>
-    <row r="150" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K150" s="7"/>
-    </row>
-    <row r="151" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K151" s="7"/>
-    </row>
-    <row r="152" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K152" s="7"/>
-    </row>
-    <row r="153" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K153" s="7"/>
-    </row>
-    <row r="154" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K154" s="7"/>
-    </row>
-    <row r="155" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K155" s="7"/>
-    </row>
-    <row r="156" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K156" s="7"/>
-    </row>
-    <row r="157" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K157" s="7"/>
-    </row>
-    <row r="158" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K158" s="7"/>
-    </row>
-    <row r="159" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K159" s="7"/>
-    </row>
-    <row r="160" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K160" s="7"/>
-    </row>
-    <row r="161" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K161" s="7"/>
-    </row>
-    <row r="162" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K162" s="7"/>
-    </row>
-    <row r="163" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K163" s="7"/>
-    </row>
-    <row r="164" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K164" s="7"/>
-    </row>
-    <row r="165" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K165" s="7"/>
-    </row>
-    <row r="166" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K166" s="7"/>
-    </row>
-    <row r="167" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K167" s="7"/>
-    </row>
-    <row r="168" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K168" s="7"/>
-    </row>
-    <row r="169" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K169" s="7"/>
-    </row>
-    <row r="170" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K170" s="7"/>
-    </row>
-    <row r="171" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K171" s="7"/>
-    </row>
-    <row r="172" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K172" s="7"/>
-    </row>
-    <row r="173" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K173" s="7"/>
-    </row>
-    <row r="174" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K174" s="7"/>
-    </row>
-    <row r="175" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K175" s="7"/>
-    </row>
-    <row r="176" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K176" s="7"/>
-    </row>
-    <row r="177" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K177" s="7"/>
-    </row>
-    <row r="178" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K178" s="7"/>
-    </row>
-    <row r="179" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K179" s="7"/>
-    </row>
-    <row r="180" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K180" s="7"/>
-    </row>
-    <row r="181" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K181" s="7"/>
-    </row>
-    <row r="182" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K182" s="7"/>
-    </row>
-    <row r="183" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K183" s="7"/>
-    </row>
-    <row r="184" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K184" s="7"/>
-    </row>
-    <row r="185" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K185" s="7"/>
-    </row>
-    <row r="186" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K186" s="7"/>
-    </row>
-    <row r="187" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K187" s="7"/>
-    </row>
-    <row r="188" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K188" s="7"/>
-    </row>
-    <row r="189" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K189" s="7"/>
-    </row>
-    <row r="190" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K190" s="7"/>
-    </row>
-    <row r="191" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K191" s="7"/>
-    </row>
-    <row r="192" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K192" s="7"/>
-    </row>
-    <row r="193" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K193" s="7"/>
-    </row>
-    <row r="194" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K194" s="7"/>
-    </row>
-    <row r="195" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K195" s="7"/>
-    </row>
-    <row r="196" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K196" s="7"/>
-    </row>
-    <row r="197" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K197" s="7"/>
-    </row>
-    <row r="198" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K198" s="7"/>
-    </row>
-    <row r="199" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K199" s="7"/>
-    </row>
-    <row r="200" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K200" s="7"/>
-    </row>
-    <row r="201" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K201" s="7"/>
-    </row>
-    <row r="202" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K202" s="7"/>
-    </row>
-    <row r="203" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K203" s="7"/>
-    </row>
-    <row r="204" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K204" s="7"/>
-    </row>
-    <row r="205" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K205" s="7"/>
-    </row>
-    <row r="206" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K206" s="7"/>
-    </row>
-    <row r="207" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K207" s="7"/>
-    </row>
-    <row r="208" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K208" s="7"/>
-    </row>
-    <row r="209" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K209" s="7"/>
-    </row>
-    <row r="210" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K210" s="7"/>
-    </row>
-    <row r="211" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K211" s="7"/>
-    </row>
-    <row r="212" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K212" s="7"/>
-    </row>
-    <row r="213" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K213" s="7"/>
-    </row>
-    <row r="214" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K214" s="7"/>
-    </row>
-    <row r="215" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K215" s="7"/>
-    </row>
-    <row r="216" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K216" s="7"/>
-    </row>
-    <row r="217" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K217" s="7"/>
-    </row>
-    <row r="218" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K218" s="7"/>
-    </row>
-    <row r="219" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K219" s="7"/>
-    </row>
-    <row r="220" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K220" s="7"/>
-    </row>
-    <row r="221" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K221" s="7"/>
-    </row>
-    <row r="222" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K222" s="7"/>
-    </row>
-    <row r="223" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K223" s="7"/>
-    </row>
-    <row r="224" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K224" s="7"/>
-    </row>
-    <row r="225" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K225" s="7"/>
-    </row>
-    <row r="226" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K226" s="7"/>
-    </row>
-    <row r="227" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K227" s="7"/>
-    </row>
-    <row r="228" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K228" s="7"/>
-    </row>
-    <row r="229" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K229" s="7"/>
-    </row>
-    <row r="230" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K230" s="7"/>
-    </row>
-    <row r="231" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K231" s="7"/>
-    </row>
-    <row r="232" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K232" s="7"/>
-    </row>
-    <row r="233" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K233" s="7"/>
-    </row>
-    <row r="234" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K234" s="7"/>
-    </row>
-    <row r="235" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K235" s="7"/>
-    </row>
-    <row r="236" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K236" s="7"/>
-    </row>
-    <row r="237" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K237" s="7"/>
-    </row>
-    <row r="238" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K238" s="7"/>
-    </row>
-    <row r="239" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K239" s="7"/>
-    </row>
-    <row r="240" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K240" s="7"/>
-    </row>
-    <row r="241" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K241" s="7"/>
-    </row>
-    <row r="242" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K242" s="7"/>
-    </row>
-    <row r="243" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K243" s="7"/>
-    </row>
-    <row r="244" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K244" s="7"/>
-    </row>
-    <row r="245" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K245" s="7"/>
-    </row>
-    <row r="246" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K246" s="7"/>
-    </row>
-    <row r="247" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K247" s="7"/>
-    </row>
-    <row r="248" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K248" s="7"/>
-    </row>
-    <row r="249" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K249" s="7"/>
-    </row>
-    <row r="250" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K250" s="7"/>
-    </row>
-    <row r="251" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K251" s="7"/>
-    </row>
-    <row r="252" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K252" s="7"/>
-    </row>
-    <row r="253" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K253" s="7"/>
-    </row>
-    <row r="254" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K254" s="7"/>
-    </row>
-    <row r="255" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K255" s="7"/>
-    </row>
-    <row r="256" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K256" s="7"/>
-    </row>
-    <row r="257" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K257" s="7"/>
-    </row>
-    <row r="258" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K258" s="7"/>
-    </row>
-    <row r="259" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K259" s="7"/>
-    </row>
-    <row r="260" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K260" s="7"/>
-    </row>
-    <row r="261" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K261" s="7"/>
-    </row>
-    <row r="262" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K262" s="7"/>
-    </row>
-    <row r="263" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K263" s="7"/>
-    </row>
-    <row r="264" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K264" s="7"/>
-    </row>
-    <row r="265" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K265" s="7"/>
-    </row>
-    <row r="266" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K266" s="7"/>
-    </row>
-    <row r="267" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K267" s="7"/>
-    </row>
-    <row r="268" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K268" s="7"/>
-    </row>
-    <row r="269" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K269" s="7"/>
-    </row>
-    <row r="270" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K270" s="7"/>
-    </row>
-    <row r="271" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K271" s="7"/>
-    </row>
-    <row r="272" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K272" s="7"/>
-    </row>
-    <row r="273" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K273" s="7"/>
-    </row>
-    <row r="274" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K274" s="7"/>
-    </row>
-    <row r="275" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K275" s="7"/>
-    </row>
-    <row r="276" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K276" s="7"/>
-    </row>
-    <row r="277" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K277" s="7"/>
-    </row>
-    <row r="278" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K278" s="7"/>
-    </row>
-    <row r="279" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K279" s="7"/>
-    </row>
-    <row r="280" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K280" s="7"/>
-    </row>
-    <row r="281" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K281" s="7"/>
-    </row>
-    <row r="282" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K282" s="7"/>
-    </row>
-    <row r="283" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K283" s="7"/>
-    </row>
-    <row r="284" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K284" s="7"/>
-    </row>
-    <row r="285" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K285" s="7"/>
-    </row>
-    <row r="286" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K286" s="7"/>
-    </row>
-    <row r="287" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K287" s="7"/>
-    </row>
-    <row r="288" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K288" s="7"/>
-    </row>
-    <row r="289" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K289" s="7"/>
-    </row>
-    <row r="290" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K290" s="7"/>
-    </row>
-    <row r="291" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K291" s="7"/>
-    </row>
-    <row r="292" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K292" s="7"/>
-    </row>
-    <row r="293" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K293" s="7"/>
-    </row>
-    <row r="294" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K294" s="7"/>
-    </row>
-    <row r="295" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K295" s="7"/>
-    </row>
-    <row r="296" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K296" s="7"/>
-    </row>
-    <row r="297" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K297" s="7"/>
-    </row>
-    <row r="298" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K298" s="7"/>
-    </row>
-    <row r="299" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K299" s="7"/>
-    </row>
-    <row r="300" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K300" s="7"/>
-    </row>
-    <row r="301" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K301" s="7"/>
-    </row>
-    <row r="302" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K302" s="7"/>
-    </row>
-    <row r="303" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K303" s="7"/>
-    </row>
-    <row r="304" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K304" s="7"/>
-    </row>
-    <row r="305" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K305" s="7"/>
-    </row>
-    <row r="306" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K306" s="7"/>
-    </row>
-    <row r="307" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K307" s="7"/>
-    </row>
-    <row r="308" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K308" s="7"/>
-    </row>
-    <row r="309" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K309" s="7"/>
-    </row>
-    <row r="310" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K310" s="7"/>
-    </row>
-    <row r="311" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K311" s="7"/>
-    </row>
-    <row r="312" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K312" s="7"/>
-    </row>
-    <row r="313" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K313" s="7"/>
-    </row>
-    <row r="314" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K314" s="7"/>
-    </row>
-    <row r="315" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K315" s="7"/>
-    </row>
-    <row r="316" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K316" s="7"/>
-    </row>
-    <row r="317" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K317" s="7"/>
-    </row>
-    <row r="318" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K318" s="7"/>
-    </row>
-    <row r="319" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K319" s="7"/>
-    </row>
-    <row r="320" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K320" s="7"/>
-    </row>
-    <row r="321" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K321" s="7"/>
-    </row>
-    <row r="322" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K322" s="7"/>
-    </row>
-    <row r="323" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K323" s="7"/>
-    </row>
-    <row r="324" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K324" s="7"/>
-    </row>
-    <row r="325" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K325" s="7"/>
-    </row>
-    <row r="326" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K326" s="7"/>
-    </row>
-    <row r="327" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K327" s="7"/>
-    </row>
-    <row r="328" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K328" s="7"/>
-    </row>
-    <row r="329" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K329" s="7"/>
-    </row>
-    <row r="330" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K330" s="7"/>
-    </row>
-    <row r="331" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K331" s="7"/>
-    </row>
-    <row r="332" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K332" s="7"/>
-    </row>
-    <row r="333" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K333" s="7"/>
-    </row>
-    <row r="334" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K334" s="7"/>
-    </row>
-    <row r="335" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K335" s="7"/>
-    </row>
-    <row r="336" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K336" s="7"/>
-    </row>
-    <row r="337" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K337" s="7"/>
-    </row>
-    <row r="338" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K338" s="7"/>
-    </row>
-    <row r="339" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K339" s="7"/>
-    </row>
-    <row r="340" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K340" s="7"/>
-    </row>
-    <row r="341" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K341" s="7"/>
-    </row>
-    <row r="342" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K342" s="7"/>
-    </row>
-    <row r="343" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K343" s="7"/>
-    </row>
-    <row r="344" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K344" s="7"/>
-    </row>
-    <row r="345" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K345" s="7"/>
-    </row>
-    <row r="346" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K346" s="7"/>
-    </row>
-    <row r="347" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K347" s="7"/>
-    </row>
-    <row r="348" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K348" s="7"/>
-    </row>
-    <row r="349" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K349" s="7"/>
-    </row>
-    <row r="350" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K350" s="7"/>
-    </row>
-    <row r="351" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K351" s="7"/>
-    </row>
-    <row r="352" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K352" s="7"/>
-    </row>
-    <row r="353" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K353" s="7"/>
-    </row>
-    <row r="354" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K354" s="7"/>
-    </row>
-    <row r="355" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K355" s="7"/>
-    </row>
-    <row r="356" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K356" s="7"/>
-    </row>
-    <row r="357" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K357" s="7"/>
-    </row>
-    <row r="358" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K358" s="7"/>
-    </row>
-    <row r="359" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K359" s="7"/>
-    </row>
-    <row r="360" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K360" s="7"/>
-    </row>
-    <row r="361" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K361" s="7"/>
-    </row>
-    <row r="362" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K362" s="7"/>
-    </row>
-    <row r="363" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K363" s="7"/>
-    </row>
-    <row r="364" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K364" s="7"/>
-    </row>
-    <row r="365" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K365" s="7"/>
-    </row>
-    <row r="366" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K366" s="7"/>
-    </row>
-    <row r="367" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K367" s="7"/>
-    </row>
-    <row r="368" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K368" s="7"/>
-    </row>
-    <row r="369" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K369" s="7"/>
-    </row>
-    <row r="370" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K370" s="7"/>
-    </row>
-    <row r="371" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K371" s="7"/>
-    </row>
-    <row r="372" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K372" s="7"/>
-    </row>
-    <row r="373" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K373" s="7"/>
-    </row>
-    <row r="374" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K374" s="7"/>
-    </row>
-    <row r="375" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K375" s="7"/>
-    </row>
-    <row r="376" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K376" s="7"/>
-    </row>
-    <row r="377" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K377" s="7"/>
-    </row>
-    <row r="378" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K378" s="7"/>
-    </row>
-    <row r="379" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K379" s="7"/>
-    </row>
-    <row r="380" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K380" s="7"/>
-    </row>
-    <row r="381" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K381" s="7"/>
-    </row>
-    <row r="382" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K382" s="7"/>
-    </row>
-    <row r="383" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K383" s="7"/>
-    </row>
-    <row r="384" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K384" s="7"/>
-    </row>
-    <row r="385" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K385" s="7"/>
-    </row>
-    <row r="386" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K386" s="7"/>
-    </row>
-    <row r="387" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K387" s="7"/>
-    </row>
-    <row r="388" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K388" s="7"/>
-    </row>
-    <row r="389" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K389" s="7"/>
-    </row>
-    <row r="390" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K390" s="7"/>
-    </row>
-    <row r="391" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K391" s="7"/>
-    </row>
-    <row r="392" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K392" s="7"/>
-    </row>
-    <row r="393" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K393" s="7"/>
-    </row>
-    <row r="394" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K394" s="7"/>
-    </row>
-    <row r="395" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K395" s="7"/>
-    </row>
-    <row r="396" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K396" s="7"/>
-    </row>
-    <row r="397" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K397" s="7"/>
-    </row>
-    <row r="398" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K398" s="7"/>
-    </row>
-    <row r="399" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K399" s="7"/>
-    </row>
-    <row r="400" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K400" s="7"/>
-    </row>
-    <row r="401" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K401" s="7"/>
-    </row>
-    <row r="402" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K402" s="7"/>
-    </row>
-    <row r="403" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K403" s="7"/>
-    </row>
-    <row r="404" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K404" s="7"/>
-    </row>
-    <row r="405" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K405" s="7"/>
-    </row>
-    <row r="406" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K406" s="7"/>
-    </row>
-    <row r="407" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K407" s="7"/>
-    </row>
-    <row r="408" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K408" s="7"/>
-    </row>
-    <row r="409" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K409" s="7"/>
-    </row>
-    <row r="410" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K410" s="7"/>
-    </row>
-    <row r="411" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K411" s="7"/>
-    </row>
-    <row r="412" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K412" s="7"/>
-    </row>
-    <row r="413" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K413" s="7"/>
-    </row>
-    <row r="414" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K414" s="7"/>
-    </row>
-    <row r="415" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K415" s="7"/>
-    </row>
-    <row r="416" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K416" s="7"/>
-    </row>
-    <row r="417" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K417" s="7"/>
-    </row>
-    <row r="418" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K418" s="7"/>
-    </row>
-    <row r="419" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K419" s="7"/>
-    </row>
-    <row r="420" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K420" s="7"/>
-    </row>
-    <row r="421" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K421" s="7"/>
-    </row>
-    <row r="422" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K422" s="7"/>
-    </row>
-    <row r="423" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K423" s="7"/>
-    </row>
-    <row r="424" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K424" s="7"/>
-    </row>
-    <row r="425" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K425" s="7"/>
-    </row>
-    <row r="426" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K426" s="7"/>
-    </row>
-    <row r="427" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K427" s="7"/>
-    </row>
-    <row r="428" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K428" s="7"/>
-    </row>
-    <row r="429" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K429" s="7"/>
-    </row>
-    <row r="430" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K430" s="7"/>
-    </row>
-    <row r="431" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K431" s="7"/>
-    </row>
-    <row r="432" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K432" s="7"/>
-    </row>
-    <row r="433" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K433" s="7"/>
-    </row>
-    <row r="434" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K434" s="7"/>
-    </row>
-    <row r="435" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K435" s="7"/>
-    </row>
-    <row r="436" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K436" s="7"/>
-    </row>
-    <row r="437" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K437" s="7"/>
-    </row>
-    <row r="438" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K438" s="7"/>
-    </row>
-    <row r="439" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K439" s="7"/>
-    </row>
-    <row r="440" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K440" s="7"/>
-    </row>
-    <row r="441" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K441" s="7"/>
-    </row>
-    <row r="442" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K442" s="7"/>
-    </row>
-    <row r="443" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K443" s="7"/>
-    </row>
-    <row r="444" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K444" s="7"/>
-    </row>
-    <row r="445" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K445" s="7"/>
-    </row>
-    <row r="446" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K446" s="7"/>
-    </row>
-    <row r="447" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K447" s="7"/>
-    </row>
-    <row r="448" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K448" s="7"/>
-    </row>
-    <row r="449" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K449" s="7"/>
-    </row>
-    <row r="450" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K450" s="7"/>
-    </row>
-    <row r="451" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K451" s="7"/>
-    </row>
-    <row r="452" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K452" s="7"/>
-    </row>
-    <row r="453" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K453" s="7"/>
-    </row>
-    <row r="454" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K454" s="7"/>
-    </row>
-    <row r="455" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K455" s="7"/>
-    </row>
-    <row r="456" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K456" s="7"/>
-    </row>
-    <row r="457" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K457" s="7"/>
-    </row>
-    <row r="458" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K458" s="7"/>
-    </row>
-    <row r="459" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K459" s="7"/>
-    </row>
-    <row r="460" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K460" s="7"/>
-    </row>
-    <row r="461" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K461" s="7"/>
-    </row>
-    <row r="462" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K462" s="7"/>
-    </row>
-    <row r="463" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K463" s="7"/>
-    </row>
-    <row r="464" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K464" s="7"/>
-    </row>
-    <row r="465" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K465" s="7"/>
-    </row>
-    <row r="466" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K466" s="7"/>
-    </row>
-    <row r="467" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K467" s="7"/>
-    </row>
-    <row r="468" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K468" s="7"/>
-    </row>
-    <row r="469" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K469" s="7"/>
-    </row>
-    <row r="470" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K470" s="7"/>
-    </row>
-    <row r="471" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K471" s="7"/>
-    </row>
-    <row r="472" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K472" s="7"/>
-    </row>
-    <row r="473" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K473" s="7"/>
-    </row>
-    <row r="474" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K474" s="7"/>
-    </row>
-    <row r="475" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K475" s="7"/>
-    </row>
-    <row r="476" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K476" s="7"/>
-    </row>
-    <row r="477" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K477" s="7"/>
-    </row>
-    <row r="478" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K478" s="7"/>
-    </row>
-    <row r="479" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K479" s="7"/>
-    </row>
-    <row r="480" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K480" s="7"/>
-    </row>
-    <row r="481" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K481" s="7"/>
-    </row>
-    <row r="482" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K482" s="7"/>
-    </row>
-    <row r="483" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K483" s="7"/>
-    </row>
-    <row r="484" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K484" s="7"/>
-    </row>
-    <row r="485" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K485" s="7"/>
-    </row>
-    <row r="486" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K486" s="7"/>
-    </row>
-    <row r="487" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K487" s="7"/>
-    </row>
-    <row r="488" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K488" s="7"/>
-    </row>
-    <row r="489" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K489" s="7"/>
-    </row>
-    <row r="490" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K490" s="7"/>
-    </row>
-    <row r="491" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K491" s="7"/>
-    </row>
-    <row r="492" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K492" s="7"/>
-    </row>
-    <row r="493" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K493" s="7"/>
-    </row>
-    <row r="494" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K494" s="7"/>
-    </row>
-    <row r="495" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K495" s="7"/>
-    </row>
-    <row r="496" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K496" s="7"/>
-    </row>
-    <row r="497" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K497" s="7"/>
-    </row>
-    <row r="498" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K498" s="7"/>
-    </row>
-    <row r="499" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K499" s="7"/>
-    </row>
-    <row r="500" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K500" s="7"/>
-    </row>
-    <row r="501" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K501" s="7"/>
-    </row>
-    <row r="502" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K502" s="7"/>
-    </row>
-    <row r="503" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K503" s="7"/>
-    </row>
-    <row r="504" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K504" s="7"/>
-    </row>
-    <row r="505" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K505" s="7"/>
-    </row>
-    <row r="506" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K506" s="7"/>
-    </row>
-    <row r="507" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K507" s="7"/>
-    </row>
-    <row r="508" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K508" s="7"/>
-    </row>
-    <row r="509" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K509" s="7"/>
-    </row>
-    <row r="510" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K510" s="7"/>
-    </row>
-    <row r="511" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K511" s="7"/>
-    </row>
-    <row r="512" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K512" s="7"/>
-    </row>
-    <row r="513" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K513" s="7"/>
-    </row>
-    <row r="514" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K514" s="7"/>
-    </row>
-    <row r="515" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K515" s="7"/>
-    </row>
-    <row r="516" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K516" s="7"/>
-    </row>
-    <row r="517" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K517" s="7"/>
-    </row>
-    <row r="518" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K518" s="7"/>
-    </row>
-    <row r="519" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K519" s="7"/>
-    </row>
-    <row r="520" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K520" s="7"/>
-    </row>
-    <row r="521" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K521" s="7"/>
-    </row>
-    <row r="522" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K522" s="7"/>
-    </row>
-    <row r="523" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K523" s="7"/>
-    </row>
-    <row r="524" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K524" s="7"/>
-    </row>
-    <row r="525" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K525" s="7"/>
-    </row>
-    <row r="526" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K526" s="7"/>
-    </row>
-    <row r="527" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K527" s="7"/>
-    </row>
-    <row r="528" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K528" s="7"/>
-    </row>
-    <row r="529" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K529" s="7"/>
-    </row>
-    <row r="530" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K530" s="7"/>
-    </row>
-    <row r="531" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K531" s="7"/>
-    </row>
-    <row r="532" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K532" s="7"/>
-    </row>
-    <row r="533" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K533" s="7"/>
-    </row>
-    <row r="534" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K534" s="7"/>
-    </row>
-    <row r="535" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K535" s="7"/>
-    </row>
-    <row r="536" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K536" s="7"/>
-    </row>
-    <row r="537" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K537" s="7"/>
-    </row>
-    <row r="538" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K538" s="7"/>
-    </row>
-    <row r="539" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K539" s="7"/>
-    </row>
-    <row r="540" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K540" s="7"/>
-    </row>
-    <row r="541" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K541" s="7"/>
-    </row>
-    <row r="542" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K542" s="7"/>
-    </row>
-    <row r="543" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K543" s="7"/>
-    </row>
-    <row r="544" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K544" s="7"/>
-    </row>
-    <row r="545" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K545" s="7"/>
-    </row>
-    <row r="546" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K546" s="7"/>
-    </row>
-    <row r="547" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K547" s="7"/>
-    </row>
-    <row r="548" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K548" s="7"/>
-    </row>
-    <row r="549" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K549" s="7"/>
-    </row>
-    <row r="550" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K550" s="7"/>
-    </row>
-    <row r="551" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K551" s="7"/>
-    </row>
-    <row r="552" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K552" s="7"/>
-    </row>
-    <row r="553" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K553" s="7"/>
-    </row>
-    <row r="554" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K554" s="7"/>
-    </row>
-    <row r="555" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K555" s="7"/>
-    </row>
-    <row r="556" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K556" s="7"/>
-    </row>
-    <row r="557" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K557" s="7"/>
-    </row>
-    <row r="558" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K558" s="7"/>
-    </row>
-    <row r="559" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K559" s="7"/>
-    </row>
-    <row r="560" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K560" s="7"/>
-    </row>
-    <row r="561" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K561" s="7"/>
-    </row>
-    <row r="562" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K562" s="7"/>
-    </row>
-    <row r="563" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K563" s="7"/>
-    </row>
-    <row r="564" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K564" s="7"/>
-    </row>
-    <row r="565" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K565" s="7"/>
-    </row>
-    <row r="566" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K566" s="7"/>
-    </row>
-    <row r="567" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K567" s="7"/>
-    </row>
-    <row r="568" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K568" s="7"/>
-    </row>
-    <row r="569" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K569" s="7"/>
-    </row>
-    <row r="570" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K570" s="7"/>
-    </row>
-    <row r="571" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K571" s="7"/>
-    </row>
-    <row r="572" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K572" s="7"/>
-    </row>
-    <row r="573" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K573" s="7"/>
-    </row>
-    <row r="574" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K574" s="7"/>
-    </row>
-    <row r="575" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K575" s="7"/>
-    </row>
-    <row r="576" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K576" s="7"/>
-    </row>
-    <row r="577" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K577" s="7"/>
-    </row>
-    <row r="578" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K578" s="7"/>
-    </row>
-    <row r="579" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K579" s="7"/>
-    </row>
-    <row r="580" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K580" s="7"/>
-    </row>
-    <row r="581" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K581" s="7"/>
-    </row>
-    <row r="582" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K582" s="7"/>
-    </row>
-    <row r="583" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K583" s="7"/>
-    </row>
-    <row r="584" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K584" s="7"/>
-    </row>
-    <row r="585" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K585" s="7"/>
-    </row>
-    <row r="586" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K586" s="7"/>
-    </row>
-    <row r="587" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K587" s="7"/>
-    </row>
-    <row r="588" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K588" s="7"/>
-    </row>
-    <row r="589" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K589" s="7"/>
-    </row>
-    <row r="590" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K590" s="7"/>
-    </row>
-    <row r="591" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K591" s="7"/>
-    </row>
-    <row r="592" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K592" s="7"/>
-    </row>
-    <row r="593" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K593" s="7"/>
-    </row>
-    <row r="594" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K594" s="7"/>
-    </row>
-    <row r="595" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K595" s="7"/>
-    </row>
-    <row r="596" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K596" s="7"/>
-    </row>
-    <row r="597" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K597" s="7"/>
-    </row>
-    <row r="598" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K598" s="7"/>
-    </row>
-    <row r="599" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K599" s="7"/>
-    </row>
-    <row r="600" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K600" s="7"/>
-    </row>
-    <row r="601" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K601" s="7"/>
-    </row>
-    <row r="602" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K602" s="7"/>
-    </row>
-    <row r="603" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K603" s="7"/>
-    </row>
-    <row r="604" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K604" s="7"/>
-    </row>
-    <row r="605" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K605" s="7"/>
-    </row>
-    <row r="606" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K606" s="7"/>
-    </row>
-    <row r="607" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K607" s="7"/>
-    </row>
-    <row r="608" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K608" s="7"/>
-    </row>
-    <row r="609" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K609" s="7"/>
-    </row>
-    <row r="610" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K610" s="7"/>
-    </row>
-    <row r="611" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K611" s="7"/>
-    </row>
-    <row r="612" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K612" s="7"/>
-    </row>
-    <row r="613" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K613" s="7"/>
-    </row>
-    <row r="614" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K614" s="7"/>
-    </row>
-    <row r="615" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K615" s="7"/>
-    </row>
-    <row r="616" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K616" s="7"/>
-    </row>
-    <row r="617" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K617" s="7"/>
-    </row>
-    <row r="618" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K618" s="7"/>
-    </row>
-    <row r="619" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K619" s="7"/>
-    </row>
-    <row r="620" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K620" s="7"/>
-    </row>
-    <row r="621" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K621" s="7"/>
-    </row>
-    <row r="622" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K622" s="7"/>
-    </row>
-    <row r="623" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K623" s="7"/>
-    </row>
-    <row r="624" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K624" s="7"/>
-    </row>
-    <row r="625" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K625" s="7"/>
-    </row>
-    <row r="626" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K626" s="7"/>
-    </row>
-    <row r="627" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K627" s="7"/>
-    </row>
-    <row r="628" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K628" s="7"/>
-    </row>
-    <row r="629" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K629" s="7"/>
-    </row>
-    <row r="630" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K630" s="7"/>
-    </row>
-    <row r="631" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K631" s="7"/>
-    </row>
-    <row r="632" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K632" s="7"/>
-    </row>
-    <row r="633" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K633" s="7"/>
-    </row>
-    <row r="634" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K634" s="7"/>
-    </row>
-    <row r="635" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K635" s="7"/>
-    </row>
-    <row r="636" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K636" s="7"/>
-    </row>
-    <row r="637" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K637" s="7"/>
-    </row>
-    <row r="638" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K638" s="7"/>
-    </row>
-    <row r="639" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K639" s="7"/>
-    </row>
-    <row r="640" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K640" s="7"/>
-    </row>
-    <row r="641" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K641" s="7"/>
-    </row>
-    <row r="642" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K642" s="7"/>
-    </row>
-    <row r="643" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K643" s="7"/>
-    </row>
-    <row r="644" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K644" s="7"/>
-    </row>
-    <row r="645" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K645" s="7"/>
-    </row>
-    <row r="646" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K646" s="7"/>
-    </row>
-    <row r="647" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K647" s="7"/>
-    </row>
-    <row r="648" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K648" s="7"/>
-    </row>
-    <row r="649" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K649" s="7"/>
-    </row>
-    <row r="650" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K650" s="7"/>
-    </row>
-    <row r="651" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K651" s="7"/>
-    </row>
-    <row r="652" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K652" s="7"/>
-    </row>
-    <row r="653" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K653" s="7"/>
-    </row>
-    <row r="654" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K654" s="7"/>
-    </row>
-    <row r="655" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K655" s="7"/>
-    </row>
-    <row r="656" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K656" s="7"/>
-    </row>
-    <row r="657" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K657" s="7"/>
-    </row>
-    <row r="658" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K658" s="7"/>
-    </row>
-    <row r="659" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K659" s="7"/>
-    </row>
-    <row r="660" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K660" s="7"/>
-    </row>
-    <row r="661" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K661" s="7"/>
-    </row>
-    <row r="662" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K662" s="7"/>
-    </row>
-    <row r="663" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K663" s="7"/>
-    </row>
-    <row r="664" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K664" s="7"/>
-    </row>
-    <row r="665" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K665" s="7"/>
-    </row>
-    <row r="666" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K666" s="7"/>
-    </row>
-    <row r="667" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K667" s="7"/>
-    </row>
-    <row r="668" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K668" s="7"/>
-    </row>
-    <row r="669" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K669" s="7"/>
-    </row>
-    <row r="670" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K670" s="7"/>
-    </row>
-    <row r="671" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K671" s="7"/>
-    </row>
-    <row r="672" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K672" s="7"/>
-    </row>
-    <row r="673" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K673" s="7"/>
-    </row>
-    <row r="674" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K674" s="7"/>
-    </row>
-    <row r="675" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K675" s="7"/>
-    </row>
-    <row r="676" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K676" s="7"/>
-    </row>
-    <row r="677" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K677" s="7"/>
-    </row>
-    <row r="678" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K678" s="7"/>
-    </row>
-    <row r="679" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K679" s="7"/>
-    </row>
-    <row r="680" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K680" s="7"/>
-    </row>
-    <row r="681" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K681" s="7"/>
-    </row>
-    <row r="682" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K682" s="7"/>
-    </row>
-    <row r="683" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K683" s="7"/>
-    </row>
-    <row r="684" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K684" s="7"/>
-    </row>
-    <row r="685" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K685" s="7"/>
-    </row>
-    <row r="686" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K686" s="7"/>
-    </row>
-    <row r="687" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K687" s="7"/>
-    </row>
-    <row r="688" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K688" s="7"/>
-    </row>
-    <row r="689" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K689" s="7"/>
-    </row>
-    <row r="690" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K690" s="7"/>
-    </row>
-    <row r="691" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K691" s="7"/>
-    </row>
-    <row r="692" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K692" s="7"/>
-    </row>
-    <row r="693" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K693" s="7"/>
-    </row>
-    <row r="694" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K694" s="7"/>
-    </row>
-    <row r="695" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K695" s="7"/>
-    </row>
-    <row r="696" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K696" s="7"/>
-    </row>
-    <row r="697" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K697" s="7"/>
-    </row>
-    <row r="698" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K698" s="7"/>
-    </row>
-    <row r="699" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K699" s="7"/>
-    </row>
-    <row r="700" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K700" s="7"/>
-    </row>
-    <row r="701" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K701" s="7"/>
-    </row>
-    <row r="702" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K702" s="7"/>
-    </row>
-    <row r="703" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K703" s="7"/>
-    </row>
-    <row r="704" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K704" s="7"/>
-    </row>
-    <row r="705" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K705" s="7"/>
-    </row>
-    <row r="706" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K706" s="7"/>
-    </row>
-    <row r="707" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K707" s="7"/>
-    </row>
-    <row r="708" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K708" s="7"/>
-    </row>
-    <row r="709" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K709" s="7"/>
-    </row>
-    <row r="710" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K710" s="7"/>
-    </row>
-    <row r="711" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K711" s="7"/>
-    </row>
-    <row r="712" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K712" s="7"/>
-    </row>
-    <row r="713" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K713" s="7"/>
-    </row>
-    <row r="714" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K714" s="7"/>
-    </row>
-    <row r="715" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K715" s="7"/>
-    </row>
-    <row r="716" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K716" s="7"/>
-    </row>
-    <row r="717" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K717" s="7"/>
-    </row>
-    <row r="718" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K718" s="7"/>
-    </row>
-    <row r="719" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K719" s="7"/>
-    </row>
-    <row r="720" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K720" s="7"/>
-    </row>
-    <row r="721" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K721" s="7"/>
-    </row>
-    <row r="722" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K722" s="7"/>
-    </row>
-    <row r="723" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K723" s="7"/>
-    </row>
-    <row r="724" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K724" s="7"/>
-    </row>
-    <row r="725" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K725" s="7"/>
-    </row>
-    <row r="726" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K726" s="7"/>
-    </row>
-    <row r="727" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K727" s="7"/>
-    </row>
-    <row r="728" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K728" s="7"/>
-    </row>
-    <row r="729" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K729" s="7"/>
-    </row>
-    <row r="730" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K730" s="7"/>
-    </row>
-    <row r="731" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K731" s="7"/>
-    </row>
-    <row r="732" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K732" s="7"/>
-    </row>
-    <row r="733" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K733" s="7"/>
-    </row>
-    <row r="734" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K734" s="7"/>
-    </row>
-    <row r="735" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K735" s="7"/>
-    </row>
-    <row r="736" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K736" s="7"/>
-    </row>
-    <row r="737" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K737" s="7"/>
-    </row>
-    <row r="738" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K738" s="7"/>
-    </row>
-    <row r="739" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K739" s="7"/>
-    </row>
-    <row r="740" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K740" s="7"/>
-    </row>
-    <row r="741" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K741" s="7"/>
-    </row>
-    <row r="742" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K742" s="7"/>
-    </row>
-    <row r="743" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K743" s="7"/>
-    </row>
-    <row r="744" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K744" s="7"/>
-    </row>
-    <row r="745" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K745" s="7"/>
-    </row>
-    <row r="746" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K746" s="7"/>
-    </row>
-    <row r="747" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K747" s="7"/>
-    </row>
-    <row r="748" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K748" s="7"/>
-    </row>
-    <row r="749" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K749" s="7"/>
-    </row>
-    <row r="750" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K750" s="7"/>
-    </row>
-    <row r="751" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K751" s="7"/>
-    </row>
-    <row r="752" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K752" s="7"/>
-    </row>
-    <row r="753" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K753" s="7"/>
-    </row>
-    <row r="754" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K754" s="7"/>
-    </row>
-    <row r="755" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K755" s="7"/>
-    </row>
-    <row r="756" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K756" s="7"/>
-    </row>
-    <row r="757" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K757" s="7"/>
-    </row>
-    <row r="758" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K758" s="7"/>
-    </row>
-    <row r="759" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K759" s="7"/>
-    </row>
-    <row r="760" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K760" s="7"/>
-    </row>
-    <row r="761" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K761" s="7"/>
-    </row>
-    <row r="762" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K762" s="7"/>
-    </row>
-    <row r="763" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K763" s="7"/>
-    </row>
-    <row r="764" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K764" s="7"/>
-    </row>
-    <row r="765" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K765" s="7"/>
-    </row>
-    <row r="766" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K766" s="7"/>
-    </row>
-    <row r="767" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K767" s="7"/>
-    </row>
-    <row r="768" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K768" s="7"/>
-    </row>
-    <row r="769" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K769" s="7"/>
-    </row>
-    <row r="770" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K770" s="7"/>
-    </row>
-    <row r="771" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K771" s="7"/>
-    </row>
-    <row r="772" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K772" s="7"/>
-    </row>
-    <row r="773" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K773" s="7"/>
-    </row>
-    <row r="774" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K774" s="7"/>
-    </row>
-    <row r="775" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K775" s="7"/>
-    </row>
-    <row r="776" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K776" s="7"/>
-    </row>
-    <row r="777" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K777" s="7"/>
-    </row>
-    <row r="778" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K778" s="7"/>
-    </row>
-    <row r="779" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K779" s="7"/>
-    </row>
-    <row r="780" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K780" s="7"/>
-    </row>
-    <row r="781" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K781" s="7"/>
-    </row>
-    <row r="782" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K782" s="7"/>
-    </row>
-    <row r="783" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K783" s="7"/>
-    </row>
-    <row r="784" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K784" s="7"/>
-    </row>
-    <row r="785" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K785" s="7"/>
-    </row>
-    <row r="786" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K786" s="7"/>
-    </row>
-    <row r="787" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K787" s="7"/>
-    </row>
-    <row r="788" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K788" s="7"/>
-    </row>
-    <row r="789" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K789" s="7"/>
-    </row>
-    <row r="790" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K790" s="7"/>
-    </row>
-    <row r="791" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K791" s="7"/>
-    </row>
-    <row r="792" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K792" s="7"/>
-    </row>
-    <row r="793" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K793" s="7"/>
-    </row>
-    <row r="794" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K794" s="7"/>
-    </row>
-    <row r="795" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K795" s="7"/>
-    </row>
-    <row r="796" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K796" s="7"/>
-    </row>
-    <row r="797" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K797" s="7"/>
-    </row>
-    <row r="798" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K798" s="7"/>
-    </row>
-    <row r="799" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K799" s="7"/>
-    </row>
-    <row r="800" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K800" s="7"/>
-    </row>
-    <row r="801" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K801" s="7"/>
-    </row>
-    <row r="802" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K802" s="7"/>
-    </row>
-    <row r="803" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K803" s="7"/>
-    </row>
-    <row r="804" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K804" s="7"/>
-    </row>
-    <row r="805" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K805" s="7"/>
-    </row>
-    <row r="806" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K806" s="7"/>
-    </row>
-    <row r="807" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K807" s="7"/>
-    </row>
-    <row r="808" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K808" s="7"/>
-    </row>
-    <row r="809" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K809" s="7"/>
-    </row>
-    <row r="810" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K810" s="7"/>
-    </row>
-    <row r="811" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K811" s="7"/>
-    </row>
-    <row r="812" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K812" s="7"/>
-    </row>
-    <row r="813" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K813" s="7"/>
-    </row>
-    <row r="814" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K814" s="7"/>
-    </row>
-    <row r="815" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K815" s="7"/>
-    </row>
-    <row r="816" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K816" s="7"/>
-    </row>
-    <row r="817" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K817" s="7"/>
-    </row>
-    <row r="818" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K818" s="7"/>
-    </row>
-    <row r="819" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K819" s="7"/>
-    </row>
-    <row r="820" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K820" s="7"/>
-    </row>
-    <row r="821" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K821" s="7"/>
-    </row>
-    <row r="822" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K822" s="7"/>
-    </row>
-    <row r="823" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K823" s="7"/>
-    </row>
-    <row r="824" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K824" s="7"/>
-    </row>
-    <row r="825" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K825" s="7"/>
-    </row>
-    <row r="826" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K826" s="7"/>
-    </row>
-    <row r="827" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K827" s="7"/>
-    </row>
-    <row r="828" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K828" s="7"/>
-    </row>
-    <row r="829" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K829" s="7"/>
-    </row>
-    <row r="830" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K830" s="7"/>
-    </row>
-    <row r="831" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K831" s="7"/>
-    </row>
-    <row r="832" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K832" s="7"/>
-    </row>
-    <row r="833" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K833" s="7"/>
-    </row>
-    <row r="834" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K834" s="7"/>
-    </row>
-    <row r="835" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K835" s="7"/>
-    </row>
-    <row r="836" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K836" s="7"/>
-    </row>
-    <row r="837" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K837" s="7"/>
-    </row>
-    <row r="838" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K838" s="7"/>
-    </row>
-    <row r="839" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K839" s="7"/>
-    </row>
-    <row r="840" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K840" s="7"/>
-    </row>
-    <row r="841" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K841" s="7"/>
-    </row>
-    <row r="842" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K842" s="7"/>
-    </row>
-    <row r="843" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K843" s="7"/>
-    </row>
-    <row r="844" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K844" s="7"/>
-    </row>
-    <row r="845" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K845" s="7"/>
-    </row>
-    <row r="846" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K846" s="7"/>
-    </row>
-    <row r="847" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K847" s="7"/>
-    </row>
-    <row r="848" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K848" s="7"/>
-    </row>
-    <row r="849" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K849" s="7"/>
-    </row>
-    <row r="850" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K850" s="7"/>
-    </row>
-    <row r="851" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K851" s="7"/>
-    </row>
-    <row r="852" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K852" s="7"/>
-    </row>
-    <row r="853" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K853" s="7"/>
-    </row>
-    <row r="854" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K854" s="7"/>
-    </row>
-    <row r="855" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K855" s="7"/>
-    </row>
-    <row r="856" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K856" s="7"/>
-    </row>
-    <row r="857" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K857" s="7"/>
-    </row>
-    <row r="858" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K858" s="7"/>
-    </row>
-    <row r="859" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K859" s="7"/>
-    </row>
-    <row r="860" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K860" s="7"/>
-    </row>
-    <row r="861" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K861" s="7"/>
-    </row>
-    <row r="862" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K862" s="7"/>
-    </row>
-    <row r="863" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K863" s="7"/>
-    </row>
-    <row r="864" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K864" s="7"/>
-    </row>
-    <row r="865" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K865" s="7"/>
-    </row>
-    <row r="866" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K866" s="7"/>
-    </row>
-    <row r="867" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K867" s="7"/>
-    </row>
-    <row r="868" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K868" s="7"/>
-    </row>
-    <row r="869" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K869" s="7"/>
-    </row>
-    <row r="870" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K870" s="7"/>
-    </row>
-    <row r="871" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K871" s="7"/>
-    </row>
-    <row r="872" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K872" s="7"/>
-    </row>
-    <row r="873" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K873" s="7"/>
-    </row>
-    <row r="874" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K874" s="7"/>
-    </row>
-    <row r="875" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K875" s="7"/>
-    </row>
-    <row r="876" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K876" s="7"/>
-    </row>
-    <row r="877" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K877" s="7"/>
-    </row>
-    <row r="878" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K878" s="7"/>
-    </row>
-    <row r="879" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K879" s="7"/>
-    </row>
-    <row r="880" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K880" s="7"/>
-    </row>
-    <row r="881" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K881" s="7"/>
-    </row>
-    <row r="882" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K882" s="7"/>
-    </row>
-    <row r="883" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K883" s="7"/>
-    </row>
-    <row r="884" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K884" s="7"/>
-    </row>
-    <row r="885" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K885" s="7"/>
-    </row>
-    <row r="886" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K886" s="7"/>
-    </row>
-    <row r="887" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K887" s="7"/>
-    </row>
-    <row r="888" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K888" s="7"/>
-    </row>
-    <row r="889" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K889" s="7"/>
-    </row>
-    <row r="890" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K890" s="7"/>
-    </row>
-    <row r="891" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K891" s="7"/>
-    </row>
-    <row r="892" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K892" s="7"/>
-    </row>
-    <row r="893" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K893" s="7"/>
-    </row>
-    <row r="894" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K894" s="7"/>
-    </row>
-    <row r="895" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K895" s="7"/>
-    </row>
-    <row r="896" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K896" s="7"/>
-    </row>
-    <row r="897" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K897" s="7"/>
-    </row>
-    <row r="898" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K898" s="7"/>
-    </row>
-    <row r="899" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K899" s="7"/>
-    </row>
-    <row r="900" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K900" s="7"/>
-    </row>
-    <row r="901" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K901" s="7"/>
-    </row>
-    <row r="902" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K902" s="7"/>
-    </row>
-    <row r="903" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K903" s="7"/>
-    </row>
-    <row r="904" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K904" s="7"/>
-    </row>
-    <row r="905" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K905" s="7"/>
-    </row>
-    <row r="906" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K906" s="7"/>
-    </row>
-    <row r="907" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K907" s="7"/>
-    </row>
-    <row r="908" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K908" s="7"/>
-    </row>
-    <row r="909" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K909" s="7"/>
-    </row>
-    <row r="910" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K910" s="7"/>
-    </row>
-    <row r="911" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K911" s="7"/>
-    </row>
-    <row r="912" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K912" s="7"/>
-    </row>
-    <row r="913" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K913" s="7"/>
-    </row>
-    <row r="914" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K914" s="7"/>
-    </row>
-    <row r="915" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K915" s="7"/>
-    </row>
-    <row r="916" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K916" s="7"/>
-    </row>
-    <row r="917" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K917" s="7"/>
-    </row>
-    <row r="918" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K918" s="7"/>
-    </row>
-    <row r="919" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K919" s="7"/>
-    </row>
-    <row r="920" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K920" s="7"/>
-    </row>
-    <row r="921" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K921" s="7"/>
-    </row>
-    <row r="922" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K922" s="7"/>
-    </row>
-    <row r="923" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K923" s="7"/>
-    </row>
-    <row r="924" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K924" s="7"/>
-    </row>
-    <row r="925" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K925" s="7"/>
-    </row>
-    <row r="926" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K926" s="7"/>
-    </row>
-    <row r="927" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K927" s="7"/>
-    </row>
-    <row r="928" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K928" s="7"/>
-    </row>
-    <row r="929" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K929" s="7"/>
-    </row>
-    <row r="930" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K930" s="7"/>
-    </row>
-    <row r="931" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K931" s="7"/>
-    </row>
-    <row r="932" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K932" s="7"/>
-    </row>
-    <row r="933" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K933" s="7"/>
-    </row>
-    <row r="934" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K934" s="7"/>
-    </row>
-    <row r="935" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K935" s="7"/>
-    </row>
-    <row r="936" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K936" s="7"/>
-    </row>
-    <row r="937" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K937" s="7"/>
-    </row>
-    <row r="938" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K938" s="7"/>
-    </row>
-    <row r="939" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K939" s="7"/>
-    </row>
-    <row r="940" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K940" s="7"/>
-    </row>
-    <row r="941" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K941" s="7"/>
-    </row>
-    <row r="942" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K942" s="7"/>
-    </row>
-    <row r="943" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K943" s="7"/>
-    </row>
-    <row r="944" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K944" s="7"/>
-    </row>
-    <row r="945" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K945" s="7"/>
-    </row>
-    <row r="946" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K946" s="7"/>
-    </row>
-    <row r="947" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K947" s="7"/>
-    </row>
-    <row r="948" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K948" s="7"/>
-    </row>
-    <row r="949" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K949" s="7"/>
-    </row>
-    <row r="950" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K950" s="7"/>
-    </row>
-    <row r="951" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K951" s="7"/>
-    </row>
-    <row r="952" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K952" s="7"/>
-    </row>
-    <row r="953" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K953" s="7"/>
-    </row>
-    <row r="954" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K954" s="7"/>
-    </row>
-    <row r="955" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K955" s="7"/>
-    </row>
-    <row r="956" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K956" s="7"/>
-    </row>
-    <row r="957" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K957" s="7"/>
-    </row>
-    <row r="958" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K958" s="7"/>
-    </row>
-    <row r="959" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K959" s="7"/>
-    </row>
-    <row r="960" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K960" s="7"/>
-    </row>
-    <row r="961" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K961" s="7"/>
-    </row>
-    <row r="962" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K962" s="7"/>
-    </row>
-    <row r="963" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K963" s="7"/>
-    </row>
-    <row r="964" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K964" s="7"/>
-    </row>
-    <row r="965" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K965" s="7"/>
-    </row>
-    <row r="966" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K966" s="7"/>
-    </row>
-    <row r="967" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K967" s="7"/>
-    </row>
-    <row r="968" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K968" s="7"/>
-    </row>
-    <row r="969" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K969" s="7"/>
-    </row>
-    <row r="970" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K970" s="7"/>
-    </row>
-    <row r="971" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K971" s="7"/>
-    </row>
-    <row r="972" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K972" s="7"/>
-    </row>
-    <row r="973" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K973" s="7"/>
-    </row>
-    <row r="974" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K974" s="7"/>
-    </row>
-    <row r="975" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K975" s="7"/>
-    </row>
-    <row r="976" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K976" s="7"/>
-    </row>
-    <row r="977" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K977" s="7"/>
-    </row>
-    <row r="978" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K978" s="7"/>
-    </row>
-    <row r="979" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K979" s="7"/>
-    </row>
-    <row r="980" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K980" s="7"/>
-    </row>
-    <row r="981" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K981" s="7"/>
-    </row>
-    <row r="982" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K982" s="7"/>
-    </row>
-    <row r="983" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K983" s="7"/>
-    </row>
-    <row r="984" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K984" s="7"/>
-    </row>
-    <row r="985" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K985" s="7"/>
-    </row>
-    <row r="986" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K986" s="7"/>
-    </row>
-    <row r="987" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K987" s="7"/>
-    </row>
-    <row r="988" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K988" s="7"/>
-    </row>
-    <row r="989" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K989" s="7"/>
-    </row>
-    <row r="990" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K990" s="7"/>
-    </row>
-    <row r="991" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K991" s="7"/>
-    </row>
-    <row r="992" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K992" s="7"/>
-    </row>
-    <row r="993" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K993" s="7"/>
-    </row>
-    <row r="994" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K994" s="7"/>
-    </row>
-    <row r="995" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K995" s="7"/>
-    </row>
-    <row r="996" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K996" s="7"/>
-    </row>
-    <row r="997" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K997" s="7"/>
-    </row>
-    <row r="998" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K998" s="7"/>
-    </row>
-    <row r="999" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K999" s="7"/>
-    </row>
-    <row r="1000" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1000" s="7"/>
-    </row>
-    <row r="1001" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1001" s="7"/>
-    </row>
-    <row r="1002" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1002" s="7"/>
-    </row>
-    <row r="1003" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1003" s="7"/>
-    </row>
-    <row r="1004" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1004" s="7"/>
-    </row>
-    <row r="1005" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1005" s="7"/>
-    </row>
-    <row r="1006" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1006" s="7"/>
-    </row>
-    <row r="1007" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1007" s="7"/>
-    </row>
-    <row r="1008" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1008" s="7"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFFBE4D5"/>
@@ -25803,6 +21712,4108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2">
+    <tabColor rgb="FFFBE4D5"/>
+  </sheetPr>
+  <dimension ref="A1:Q1008"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" customWidth="1"/>
+    <col min="4" max="5" width="4.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" customWidth="1"/>
+    <col min="11" max="11" width="29.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="29" width="9.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>444</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="14" t="str">
+        <f>"宿部屋"&amp;".webp"</f>
+        <v>宿部屋.webp</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:13" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>439</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>441</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="6"/>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="D13" s="18">
+        <v>258</v>
+      </c>
+      <c r="E13" s="18">
+        <v>137</v>
+      </c>
+      <c r="F13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="M13" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="B14" t="s">
+        <v>446</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="18">
+        <v>231</v>
+      </c>
+      <c r="E14" s="18">
+        <v>134</v>
+      </c>
+      <c r="F14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="M14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="D15" s="18">
+        <v>264.5</v>
+      </c>
+      <c r="E15" s="18">
+        <v>163</v>
+      </c>
+      <c r="F15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="B16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="18">
+        <v>236</v>
+      </c>
+      <c r="E16" s="18">
+        <v>157</v>
+      </c>
+      <c r="F16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="M16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="B17" t="s">
+        <v>447</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="18">
+        <v>248</v>
+      </c>
+      <c r="E17" s="18">
+        <v>133</v>
+      </c>
+      <c r="F17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="str">
+        <f t="shared" ref="G17:G23" si="0">A17&amp;".webp"</f>
+        <v>森農場.webp</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>502</v>
+      </c>
+      <c r="M17" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>495</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>畑.webp</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="B19" t="s">
+        <v>448</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="18">
+        <v>251</v>
+      </c>
+      <c r="E19" s="18">
+        <v>142</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>水脈森.webp</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="M19" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>480</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="18">
+        <v>253</v>
+      </c>
+      <c r="E20" s="18">
+        <v>155</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>獣の森.webp</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>509</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>獣の森・水辺.webp</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="J21" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K21" s="18"/>
+      <c r="M21" s="6"/>
+    </row>
+    <row r="22" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>獣の森・森林.webp</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="J22" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K22" s="18"/>
+      <c r="M22" s="6"/>
+    </row>
+    <row r="23" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>505</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>獣の森・沼地.webp</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="J23" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K23" s="18"/>
+      <c r="M23" s="6"/>
+    </row>
+    <row r="24" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="18"/>
+      <c r="M24" s="6"/>
+    </row>
+    <row r="25" spans="1:17" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="18"/>
+      <c r="M25" s="6"/>
+    </row>
+    <row r="26" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="18"/>
+      <c r="M26" s="6"/>
+    </row>
+    <row r="27" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="B27" t="s">
+        <v>450</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="18">
+        <v>269</v>
+      </c>
+      <c r="E27" s="18">
+        <v>118</v>
+      </c>
+      <c r="F27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14" t="str">
+        <f t="shared" ref="G27:G32" si="1">A27&amp;".webp"</f>
+        <v>負の跡地.webp</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="M27" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="B28" t="s">
+        <v>451</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="18">
+        <v>232</v>
+      </c>
+      <c r="E28" s="18">
+        <v>120</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>海沿いの森.webp</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="M28" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="B29" t="s">
+        <v>456</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29" s="18">
+        <v>255</v>
+      </c>
+      <c r="E29" s="18">
+        <v>178</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>大鉱山.webp</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="M29" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="B30" t="s">
+        <v>452</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="D30" s="18">
+        <v>324</v>
+      </c>
+      <c r="E30" s="18">
+        <v>130</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>大森林.webp</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="M30" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="B31" t="s">
+        <v>453</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31" s="18">
+        <v>253</v>
+      </c>
+      <c r="E31" s="18">
+        <v>95</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>砂漠山.webp</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="M31" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="B32" t="s">
+        <v>454</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="D32" s="18">
+        <v>295</v>
+      </c>
+      <c r="E32" s="18">
+        <v>90</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>戦場後.webp</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="M32" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="B33" t="s">
+        <v>433</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="18">
+        <v>264</v>
+      </c>
+      <c r="E33" s="18">
+        <v>66</v>
+      </c>
+      <c r="F33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="M33" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>489</v>
+      </c>
+      <c r="B34" t="s">
+        <v>455</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="D34" s="18">
+        <v>268</v>
+      </c>
+      <c r="E34" s="18">
+        <v>189</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="M34" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>457</v>
+      </c>
+      <c r="B35" t="s">
+        <v>458</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="D35">
+        <v>283</v>
+      </c>
+      <c r="E35">
+        <v>207</v>
+      </c>
+      <c r="F35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" s="7"/>
+      <c r="M35" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>459</v>
+      </c>
+      <c r="B36" t="s">
+        <v>460</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="D36">
+        <v>315.5</v>
+      </c>
+      <c r="E36">
+        <v>218</v>
+      </c>
+      <c r="F36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="M36" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>461</v>
+      </c>
+      <c r="B37" t="s">
+        <v>462</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="D37">
+        <v>341</v>
+      </c>
+      <c r="E37">
+        <v>207</v>
+      </c>
+      <c r="F37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="7"/>
+      <c r="M37" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>463</v>
+      </c>
+      <c r="B38" t="s">
+        <v>464</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="D38">
+        <v>341</v>
+      </c>
+      <c r="E38">
+        <v>225</v>
+      </c>
+      <c r="F38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7"/>
+      <c r="M38" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>465</v>
+      </c>
+      <c r="B39" t="s">
+        <v>465</v>
+      </c>
+      <c r="C39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39">
+        <v>381</v>
+      </c>
+      <c r="E39">
+        <v>121</v>
+      </c>
+      <c r="F39" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="M39" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>466</v>
+      </c>
+      <c r="B40" t="s">
+        <v>467</v>
+      </c>
+      <c r="C40" t="s">
+        <v>472</v>
+      </c>
+      <c r="D40">
+        <v>483</v>
+      </c>
+      <c r="E40">
+        <v>86</v>
+      </c>
+      <c r="F40" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" s="7"/>
+      <c r="M40" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>468</v>
+      </c>
+      <c r="B41" t="s">
+        <v>469</v>
+      </c>
+      <c r="C41" t="s">
+        <v>205</v>
+      </c>
+      <c r="D41">
+        <v>488</v>
+      </c>
+      <c r="E41">
+        <v>77</v>
+      </c>
+      <c r="F41" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7"/>
+      <c r="M41" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>470</v>
+      </c>
+      <c r="B42" t="s">
+        <v>471</v>
+      </c>
+      <c r="C42" t="s">
+        <v>472</v>
+      </c>
+      <c r="D42">
+        <v>333</v>
+      </c>
+      <c r="E42">
+        <v>353</v>
+      </c>
+      <c r="F42" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7"/>
+      <c r="M42" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>473</v>
+      </c>
+      <c r="B43" t="s">
+        <v>474</v>
+      </c>
+      <c r="C43" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43">
+        <v>289</v>
+      </c>
+      <c r="E43">
+        <v>493</v>
+      </c>
+      <c r="F43" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7"/>
+      <c r="M43" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="B44" t="s">
+        <v>475</v>
+      </c>
+      <c r="C44" t="s">
+        <v>472</v>
+      </c>
+      <c r="D44">
+        <v>222.5</v>
+      </c>
+      <c r="E44">
+        <v>352</v>
+      </c>
+      <c r="F44" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" s="7"/>
+      <c r="M44" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K45" s="7"/>
+    </row>
+    <row r="46" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="7"/>
+    </row>
+    <row r="47" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K47" s="7"/>
+    </row>
+    <row r="48" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K48" s="7"/>
+    </row>
+    <row r="49" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K49" s="7"/>
+    </row>
+    <row r="50" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K51" s="7"/>
+    </row>
+    <row r="52" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K52" s="7"/>
+    </row>
+    <row r="53" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K53" s="7"/>
+    </row>
+    <row r="54" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K54" s="7"/>
+    </row>
+    <row r="55" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K55" s="7"/>
+    </row>
+    <row r="56" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K56" s="7"/>
+    </row>
+    <row r="57" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K57" s="7"/>
+    </row>
+    <row r="58" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K58" s="7"/>
+    </row>
+    <row r="59" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K59" s="7"/>
+    </row>
+    <row r="60" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K60" s="7"/>
+    </row>
+    <row r="61" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K61" s="7"/>
+    </row>
+    <row r="62" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K62" s="7"/>
+    </row>
+    <row r="63" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K63" s="7"/>
+    </row>
+    <row r="64" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K64" s="7"/>
+    </row>
+    <row r="65" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K65" s="7"/>
+    </row>
+    <row r="66" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K66" s="7"/>
+    </row>
+    <row r="67" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K67" s="7"/>
+    </row>
+    <row r="68" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K68" s="7"/>
+    </row>
+    <row r="69" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K69" s="7"/>
+    </row>
+    <row r="70" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K70" s="7"/>
+    </row>
+    <row r="71" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K71" s="7"/>
+    </row>
+    <row r="72" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K72" s="7"/>
+    </row>
+    <row r="73" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K73" s="7"/>
+    </row>
+    <row r="74" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K74" s="7"/>
+    </row>
+    <row r="75" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K75" s="7"/>
+    </row>
+    <row r="76" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K76" s="7"/>
+    </row>
+    <row r="77" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K77" s="7"/>
+    </row>
+    <row r="78" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K78" s="7"/>
+    </row>
+    <row r="79" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K79" s="7"/>
+    </row>
+    <row r="80" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K80" s="7"/>
+    </row>
+    <row r="81" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K81" s="7"/>
+    </row>
+    <row r="82" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K82" s="7"/>
+    </row>
+    <row r="83" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K83" s="7"/>
+    </row>
+    <row r="84" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K84" s="7"/>
+    </row>
+    <row r="85" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K85" s="7"/>
+    </row>
+    <row r="86" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K86" s="7"/>
+    </row>
+    <row r="87" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K87" s="7"/>
+    </row>
+    <row r="88" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K88" s="7"/>
+    </row>
+    <row r="89" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K89" s="7"/>
+    </row>
+    <row r="90" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K90" s="7"/>
+    </row>
+    <row r="91" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K91" s="7"/>
+    </row>
+    <row r="92" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K92" s="7"/>
+    </row>
+    <row r="93" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K93" s="7"/>
+    </row>
+    <row r="94" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K94" s="7"/>
+    </row>
+    <row r="95" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K95" s="7"/>
+    </row>
+    <row r="96" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K96" s="7"/>
+    </row>
+    <row r="97" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K97" s="7"/>
+    </row>
+    <row r="98" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K98" s="7"/>
+    </row>
+    <row r="99" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K99" s="7"/>
+    </row>
+    <row r="100" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K100" s="7"/>
+    </row>
+    <row r="101" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K101" s="7"/>
+    </row>
+    <row r="102" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K102" s="7"/>
+    </row>
+    <row r="103" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K103" s="7"/>
+    </row>
+    <row r="104" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K104" s="7"/>
+    </row>
+    <row r="105" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K105" s="7"/>
+    </row>
+    <row r="106" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K106" s="7"/>
+    </row>
+    <row r="107" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K107" s="7"/>
+    </row>
+    <row r="108" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K108" s="7"/>
+    </row>
+    <row r="109" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K109" s="7"/>
+    </row>
+    <row r="110" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K110" s="7"/>
+    </row>
+    <row r="111" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K111" s="7"/>
+    </row>
+    <row r="112" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K112" s="7"/>
+    </row>
+    <row r="113" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K113" s="7"/>
+    </row>
+    <row r="114" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K114" s="7"/>
+    </row>
+    <row r="115" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K115" s="7"/>
+    </row>
+    <row r="116" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K116" s="7"/>
+    </row>
+    <row r="117" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K117" s="7"/>
+    </row>
+    <row r="118" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K118" s="7"/>
+    </row>
+    <row r="119" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K119" s="7"/>
+    </row>
+    <row r="120" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K120" s="7"/>
+    </row>
+    <row r="121" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K121" s="7"/>
+    </row>
+    <row r="122" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K122" s="7"/>
+    </row>
+    <row r="123" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K123" s="7"/>
+    </row>
+    <row r="124" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K124" s="7"/>
+    </row>
+    <row r="125" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K125" s="7"/>
+    </row>
+    <row r="126" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K126" s="7"/>
+    </row>
+    <row r="127" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K127" s="7"/>
+    </row>
+    <row r="128" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K128" s="7"/>
+    </row>
+    <row r="129" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K129" s="7"/>
+    </row>
+    <row r="130" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K130" s="7"/>
+    </row>
+    <row r="131" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K131" s="7"/>
+    </row>
+    <row r="132" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K132" s="7"/>
+    </row>
+    <row r="133" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K133" s="7"/>
+    </row>
+    <row r="134" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K134" s="7"/>
+    </row>
+    <row r="135" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K135" s="7"/>
+    </row>
+    <row r="136" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K136" s="7"/>
+    </row>
+    <row r="137" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K137" s="7"/>
+    </row>
+    <row r="138" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K138" s="7"/>
+    </row>
+    <row r="139" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K139" s="7"/>
+    </row>
+    <row r="140" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K140" s="7"/>
+    </row>
+    <row r="141" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K141" s="7"/>
+    </row>
+    <row r="142" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K142" s="7"/>
+    </row>
+    <row r="143" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K143" s="7"/>
+    </row>
+    <row r="144" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K144" s="7"/>
+    </row>
+    <row r="145" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K145" s="7"/>
+    </row>
+    <row r="146" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K146" s="7"/>
+    </row>
+    <row r="147" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K147" s="7"/>
+    </row>
+    <row r="148" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K148" s="7"/>
+    </row>
+    <row r="149" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K149" s="7"/>
+    </row>
+    <row r="150" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K150" s="7"/>
+    </row>
+    <row r="151" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K151" s="7"/>
+    </row>
+    <row r="152" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K152" s="7"/>
+    </row>
+    <row r="153" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K153" s="7"/>
+    </row>
+    <row r="154" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K154" s="7"/>
+    </row>
+    <row r="155" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K155" s="7"/>
+    </row>
+    <row r="156" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K156" s="7"/>
+    </row>
+    <row r="157" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K157" s="7"/>
+    </row>
+    <row r="158" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K158" s="7"/>
+    </row>
+    <row r="159" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K159" s="7"/>
+    </row>
+    <row r="160" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K160" s="7"/>
+    </row>
+    <row r="161" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K161" s="7"/>
+    </row>
+    <row r="162" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K162" s="7"/>
+    </row>
+    <row r="163" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K163" s="7"/>
+    </row>
+    <row r="164" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K164" s="7"/>
+    </row>
+    <row r="165" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K165" s="7"/>
+    </row>
+    <row r="166" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K166" s="7"/>
+    </row>
+    <row r="167" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K167" s="7"/>
+    </row>
+    <row r="168" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K168" s="7"/>
+    </row>
+    <row r="169" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K169" s="7"/>
+    </row>
+    <row r="170" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K170" s="7"/>
+    </row>
+    <row r="171" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K171" s="7"/>
+    </row>
+    <row r="172" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K172" s="7"/>
+    </row>
+    <row r="173" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K173" s="7"/>
+    </row>
+    <row r="174" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K174" s="7"/>
+    </row>
+    <row r="175" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K175" s="7"/>
+    </row>
+    <row r="176" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K176" s="7"/>
+    </row>
+    <row r="177" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K177" s="7"/>
+    </row>
+    <row r="178" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K178" s="7"/>
+    </row>
+    <row r="179" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K179" s="7"/>
+    </row>
+    <row r="180" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K180" s="7"/>
+    </row>
+    <row r="181" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K181" s="7"/>
+    </row>
+    <row r="182" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K182" s="7"/>
+    </row>
+    <row r="183" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K183" s="7"/>
+    </row>
+    <row r="184" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K184" s="7"/>
+    </row>
+    <row r="185" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K185" s="7"/>
+    </row>
+    <row r="186" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K186" s="7"/>
+    </row>
+    <row r="187" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K187" s="7"/>
+    </row>
+    <row r="188" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K188" s="7"/>
+    </row>
+    <row r="189" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K189" s="7"/>
+    </row>
+    <row r="190" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K190" s="7"/>
+    </row>
+    <row r="191" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K191" s="7"/>
+    </row>
+    <row r="192" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K192" s="7"/>
+    </row>
+    <row r="193" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K193" s="7"/>
+    </row>
+    <row r="194" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K194" s="7"/>
+    </row>
+    <row r="195" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K195" s="7"/>
+    </row>
+    <row r="196" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K196" s="7"/>
+    </row>
+    <row r="197" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K197" s="7"/>
+    </row>
+    <row r="198" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K198" s="7"/>
+    </row>
+    <row r="199" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K199" s="7"/>
+    </row>
+    <row r="200" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K200" s="7"/>
+    </row>
+    <row r="201" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K201" s="7"/>
+    </row>
+    <row r="202" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K202" s="7"/>
+    </row>
+    <row r="203" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K203" s="7"/>
+    </row>
+    <row r="204" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K204" s="7"/>
+    </row>
+    <row r="205" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K205" s="7"/>
+    </row>
+    <row r="206" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K206" s="7"/>
+    </row>
+    <row r="207" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K207" s="7"/>
+    </row>
+    <row r="208" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K208" s="7"/>
+    </row>
+    <row r="209" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K209" s="7"/>
+    </row>
+    <row r="210" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K210" s="7"/>
+    </row>
+    <row r="211" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K211" s="7"/>
+    </row>
+    <row r="212" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K212" s="7"/>
+    </row>
+    <row r="213" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K213" s="7"/>
+    </row>
+    <row r="214" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K214" s="7"/>
+    </row>
+    <row r="215" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K215" s="7"/>
+    </row>
+    <row r="216" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K216" s="7"/>
+    </row>
+    <row r="217" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K217" s="7"/>
+    </row>
+    <row r="218" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K218" s="7"/>
+    </row>
+    <row r="219" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K219" s="7"/>
+    </row>
+    <row r="220" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K220" s="7"/>
+    </row>
+    <row r="221" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K221" s="7"/>
+    </row>
+    <row r="222" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K222" s="7"/>
+    </row>
+    <row r="223" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K223" s="7"/>
+    </row>
+    <row r="224" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K224" s="7"/>
+    </row>
+    <row r="225" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K225" s="7"/>
+    </row>
+    <row r="226" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K226" s="7"/>
+    </row>
+    <row r="227" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K227" s="7"/>
+    </row>
+    <row r="228" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K228" s="7"/>
+    </row>
+    <row r="229" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K229" s="7"/>
+    </row>
+    <row r="230" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K230" s="7"/>
+    </row>
+    <row r="231" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K231" s="7"/>
+    </row>
+    <row r="232" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K232" s="7"/>
+    </row>
+    <row r="233" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K233" s="7"/>
+    </row>
+    <row r="234" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K234" s="7"/>
+    </row>
+    <row r="235" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K235" s="7"/>
+    </row>
+    <row r="236" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K236" s="7"/>
+    </row>
+    <row r="237" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K237" s="7"/>
+    </row>
+    <row r="238" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K238" s="7"/>
+    </row>
+    <row r="239" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K239" s="7"/>
+    </row>
+    <row r="240" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K240" s="7"/>
+    </row>
+    <row r="241" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K241" s="7"/>
+    </row>
+    <row r="242" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K242" s="7"/>
+    </row>
+    <row r="243" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K243" s="7"/>
+    </row>
+    <row r="244" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K244" s="7"/>
+    </row>
+    <row r="245" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K245" s="7"/>
+    </row>
+    <row r="246" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K246" s="7"/>
+    </row>
+    <row r="247" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K247" s="7"/>
+    </row>
+    <row r="248" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K248" s="7"/>
+    </row>
+    <row r="249" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K249" s="7"/>
+    </row>
+    <row r="250" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K250" s="7"/>
+    </row>
+    <row r="251" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K251" s="7"/>
+    </row>
+    <row r="252" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K252" s="7"/>
+    </row>
+    <row r="253" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K253" s="7"/>
+    </row>
+    <row r="254" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K254" s="7"/>
+    </row>
+    <row r="255" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K255" s="7"/>
+    </row>
+    <row r="256" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K256" s="7"/>
+    </row>
+    <row r="257" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K257" s="7"/>
+    </row>
+    <row r="258" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K258" s="7"/>
+    </row>
+    <row r="259" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K259" s="7"/>
+    </row>
+    <row r="260" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K260" s="7"/>
+    </row>
+    <row r="261" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K261" s="7"/>
+    </row>
+    <row r="262" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K262" s="7"/>
+    </row>
+    <row r="263" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K263" s="7"/>
+    </row>
+    <row r="264" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K264" s="7"/>
+    </row>
+    <row r="265" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K265" s="7"/>
+    </row>
+    <row r="266" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K266" s="7"/>
+    </row>
+    <row r="267" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K267" s="7"/>
+    </row>
+    <row r="268" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K268" s="7"/>
+    </row>
+    <row r="269" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K269" s="7"/>
+    </row>
+    <row r="270" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K270" s="7"/>
+    </row>
+    <row r="271" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K271" s="7"/>
+    </row>
+    <row r="272" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K272" s="7"/>
+    </row>
+    <row r="273" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K273" s="7"/>
+    </row>
+    <row r="274" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K274" s="7"/>
+    </row>
+    <row r="275" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K275" s="7"/>
+    </row>
+    <row r="276" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K276" s="7"/>
+    </row>
+    <row r="277" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K277" s="7"/>
+    </row>
+    <row r="278" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K278" s="7"/>
+    </row>
+    <row r="279" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K279" s="7"/>
+    </row>
+    <row r="280" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K280" s="7"/>
+    </row>
+    <row r="281" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K281" s="7"/>
+    </row>
+    <row r="282" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K282" s="7"/>
+    </row>
+    <row r="283" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K283" s="7"/>
+    </row>
+    <row r="284" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K284" s="7"/>
+    </row>
+    <row r="285" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K285" s="7"/>
+    </row>
+    <row r="286" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K286" s="7"/>
+    </row>
+    <row r="287" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K287" s="7"/>
+    </row>
+    <row r="288" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K288" s="7"/>
+    </row>
+    <row r="289" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K289" s="7"/>
+    </row>
+    <row r="290" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K290" s="7"/>
+    </row>
+    <row r="291" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K291" s="7"/>
+    </row>
+    <row r="292" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K292" s="7"/>
+    </row>
+    <row r="293" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K293" s="7"/>
+    </row>
+    <row r="294" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K294" s="7"/>
+    </row>
+    <row r="295" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K295" s="7"/>
+    </row>
+    <row r="296" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K296" s="7"/>
+    </row>
+    <row r="297" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K297" s="7"/>
+    </row>
+    <row r="298" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K298" s="7"/>
+    </row>
+    <row r="299" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K299" s="7"/>
+    </row>
+    <row r="300" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K300" s="7"/>
+    </row>
+    <row r="301" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K301" s="7"/>
+    </row>
+    <row r="302" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K302" s="7"/>
+    </row>
+    <row r="303" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K303" s="7"/>
+    </row>
+    <row r="304" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K304" s="7"/>
+    </row>
+    <row r="305" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K305" s="7"/>
+    </row>
+    <row r="306" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K306" s="7"/>
+    </row>
+    <row r="307" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K307" s="7"/>
+    </row>
+    <row r="308" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K308" s="7"/>
+    </row>
+    <row r="309" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K309" s="7"/>
+    </row>
+    <row r="310" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K310" s="7"/>
+    </row>
+    <row r="311" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K311" s="7"/>
+    </row>
+    <row r="312" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K312" s="7"/>
+    </row>
+    <row r="313" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K313" s="7"/>
+    </row>
+    <row r="314" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K314" s="7"/>
+    </row>
+    <row r="315" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K315" s="7"/>
+    </row>
+    <row r="316" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K316" s="7"/>
+    </row>
+    <row r="317" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K317" s="7"/>
+    </row>
+    <row r="318" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K318" s="7"/>
+    </row>
+    <row r="319" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K319" s="7"/>
+    </row>
+    <row r="320" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K320" s="7"/>
+    </row>
+    <row r="321" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K321" s="7"/>
+    </row>
+    <row r="322" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K322" s="7"/>
+    </row>
+    <row r="323" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K323" s="7"/>
+    </row>
+    <row r="324" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K324" s="7"/>
+    </row>
+    <row r="325" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K325" s="7"/>
+    </row>
+    <row r="326" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K326" s="7"/>
+    </row>
+    <row r="327" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K327" s="7"/>
+    </row>
+    <row r="328" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K328" s="7"/>
+    </row>
+    <row r="329" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K329" s="7"/>
+    </row>
+    <row r="330" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K330" s="7"/>
+    </row>
+    <row r="331" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K331" s="7"/>
+    </row>
+    <row r="332" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K332" s="7"/>
+    </row>
+    <row r="333" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K333" s="7"/>
+    </row>
+    <row r="334" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K334" s="7"/>
+    </row>
+    <row r="335" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K335" s="7"/>
+    </row>
+    <row r="336" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K336" s="7"/>
+    </row>
+    <row r="337" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K337" s="7"/>
+    </row>
+    <row r="338" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K338" s="7"/>
+    </row>
+    <row r="339" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K339" s="7"/>
+    </row>
+    <row r="340" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K340" s="7"/>
+    </row>
+    <row r="341" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K341" s="7"/>
+    </row>
+    <row r="342" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K342" s="7"/>
+    </row>
+    <row r="343" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K343" s="7"/>
+    </row>
+    <row r="344" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K344" s="7"/>
+    </row>
+    <row r="345" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K345" s="7"/>
+    </row>
+    <row r="346" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K346" s="7"/>
+    </row>
+    <row r="347" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K347" s="7"/>
+    </row>
+    <row r="348" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K348" s="7"/>
+    </row>
+    <row r="349" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K349" s="7"/>
+    </row>
+    <row r="350" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K350" s="7"/>
+    </row>
+    <row r="351" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K351" s="7"/>
+    </row>
+    <row r="352" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K352" s="7"/>
+    </row>
+    <row r="353" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K353" s="7"/>
+    </row>
+    <row r="354" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K354" s="7"/>
+    </row>
+    <row r="355" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K355" s="7"/>
+    </row>
+    <row r="356" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K356" s="7"/>
+    </row>
+    <row r="357" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K357" s="7"/>
+    </row>
+    <row r="358" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K358" s="7"/>
+    </row>
+    <row r="359" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K359" s="7"/>
+    </row>
+    <row r="360" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K360" s="7"/>
+    </row>
+    <row r="361" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K361" s="7"/>
+    </row>
+    <row r="362" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K362" s="7"/>
+    </row>
+    <row r="363" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K363" s="7"/>
+    </row>
+    <row r="364" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K364" s="7"/>
+    </row>
+    <row r="365" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K365" s="7"/>
+    </row>
+    <row r="366" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K366" s="7"/>
+    </row>
+    <row r="367" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K367" s="7"/>
+    </row>
+    <row r="368" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K368" s="7"/>
+    </row>
+    <row r="369" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K369" s="7"/>
+    </row>
+    <row r="370" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K370" s="7"/>
+    </row>
+    <row r="371" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K371" s="7"/>
+    </row>
+    <row r="372" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K372" s="7"/>
+    </row>
+    <row r="373" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K373" s="7"/>
+    </row>
+    <row r="374" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K374" s="7"/>
+    </row>
+    <row r="375" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K375" s="7"/>
+    </row>
+    <row r="376" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K376" s="7"/>
+    </row>
+    <row r="377" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K377" s="7"/>
+    </row>
+    <row r="378" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K378" s="7"/>
+    </row>
+    <row r="379" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K379" s="7"/>
+    </row>
+    <row r="380" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K380" s="7"/>
+    </row>
+    <row r="381" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K381" s="7"/>
+    </row>
+    <row r="382" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K382" s="7"/>
+    </row>
+    <row r="383" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K383" s="7"/>
+    </row>
+    <row r="384" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K384" s="7"/>
+    </row>
+    <row r="385" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K385" s="7"/>
+    </row>
+    <row r="386" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K386" s="7"/>
+    </row>
+    <row r="387" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K387" s="7"/>
+    </row>
+    <row r="388" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K388" s="7"/>
+    </row>
+    <row r="389" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K389" s="7"/>
+    </row>
+    <row r="390" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K390" s="7"/>
+    </row>
+    <row r="391" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K391" s="7"/>
+    </row>
+    <row r="392" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K392" s="7"/>
+    </row>
+    <row r="393" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K393" s="7"/>
+    </row>
+    <row r="394" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K394" s="7"/>
+    </row>
+    <row r="395" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K395" s="7"/>
+    </row>
+    <row r="396" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K396" s="7"/>
+    </row>
+    <row r="397" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K397" s="7"/>
+    </row>
+    <row r="398" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K398" s="7"/>
+    </row>
+    <row r="399" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K399" s="7"/>
+    </row>
+    <row r="400" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K400" s="7"/>
+    </row>
+    <row r="401" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K401" s="7"/>
+    </row>
+    <row r="402" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K402" s="7"/>
+    </row>
+    <row r="403" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K403" s="7"/>
+    </row>
+    <row r="404" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K404" s="7"/>
+    </row>
+    <row r="405" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K405" s="7"/>
+    </row>
+    <row r="406" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K406" s="7"/>
+    </row>
+    <row r="407" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K407" s="7"/>
+    </row>
+    <row r="408" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K408" s="7"/>
+    </row>
+    <row r="409" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K409" s="7"/>
+    </row>
+    <row r="410" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K410" s="7"/>
+    </row>
+    <row r="411" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K411" s="7"/>
+    </row>
+    <row r="412" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K412" s="7"/>
+    </row>
+    <row r="413" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K413" s="7"/>
+    </row>
+    <row r="414" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K414" s="7"/>
+    </row>
+    <row r="415" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K415" s="7"/>
+    </row>
+    <row r="416" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K416" s="7"/>
+    </row>
+    <row r="417" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K417" s="7"/>
+    </row>
+    <row r="418" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K418" s="7"/>
+    </row>
+    <row r="419" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K419" s="7"/>
+    </row>
+    <row r="420" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K420" s="7"/>
+    </row>
+    <row r="421" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K421" s="7"/>
+    </row>
+    <row r="422" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K422" s="7"/>
+    </row>
+    <row r="423" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K423" s="7"/>
+    </row>
+    <row r="424" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K424" s="7"/>
+    </row>
+    <row r="425" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K425" s="7"/>
+    </row>
+    <row r="426" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K426" s="7"/>
+    </row>
+    <row r="427" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K427" s="7"/>
+    </row>
+    <row r="428" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K428" s="7"/>
+    </row>
+    <row r="429" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K429" s="7"/>
+    </row>
+    <row r="430" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K430" s="7"/>
+    </row>
+    <row r="431" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K431" s="7"/>
+    </row>
+    <row r="432" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K432" s="7"/>
+    </row>
+    <row r="433" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K433" s="7"/>
+    </row>
+    <row r="434" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K434" s="7"/>
+    </row>
+    <row r="435" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K435" s="7"/>
+    </row>
+    <row r="436" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K436" s="7"/>
+    </row>
+    <row r="437" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K437" s="7"/>
+    </row>
+    <row r="438" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K438" s="7"/>
+    </row>
+    <row r="439" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K439" s="7"/>
+    </row>
+    <row r="440" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K440" s="7"/>
+    </row>
+    <row r="441" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K441" s="7"/>
+    </row>
+    <row r="442" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K442" s="7"/>
+    </row>
+    <row r="443" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K443" s="7"/>
+    </row>
+    <row r="444" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K444" s="7"/>
+    </row>
+    <row r="445" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K445" s="7"/>
+    </row>
+    <row r="446" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K446" s="7"/>
+    </row>
+    <row r="447" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K447" s="7"/>
+    </row>
+    <row r="448" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K448" s="7"/>
+    </row>
+    <row r="449" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K449" s="7"/>
+    </row>
+    <row r="450" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K450" s="7"/>
+    </row>
+    <row r="451" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K451" s="7"/>
+    </row>
+    <row r="452" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K452" s="7"/>
+    </row>
+    <row r="453" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K453" s="7"/>
+    </row>
+    <row r="454" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K454" s="7"/>
+    </row>
+    <row r="455" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K455" s="7"/>
+    </row>
+    <row r="456" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K456" s="7"/>
+    </row>
+    <row r="457" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K457" s="7"/>
+    </row>
+    <row r="458" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K458" s="7"/>
+    </row>
+    <row r="459" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K459" s="7"/>
+    </row>
+    <row r="460" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K460" s="7"/>
+    </row>
+    <row r="461" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K461" s="7"/>
+    </row>
+    <row r="462" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K462" s="7"/>
+    </row>
+    <row r="463" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K463" s="7"/>
+    </row>
+    <row r="464" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K464" s="7"/>
+    </row>
+    <row r="465" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K465" s="7"/>
+    </row>
+    <row r="466" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K466" s="7"/>
+    </row>
+    <row r="467" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K467" s="7"/>
+    </row>
+    <row r="468" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K468" s="7"/>
+    </row>
+    <row r="469" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K469" s="7"/>
+    </row>
+    <row r="470" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K470" s="7"/>
+    </row>
+    <row r="471" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K471" s="7"/>
+    </row>
+    <row r="472" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K472" s="7"/>
+    </row>
+    <row r="473" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K473" s="7"/>
+    </row>
+    <row r="474" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K474" s="7"/>
+    </row>
+    <row r="475" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K475" s="7"/>
+    </row>
+    <row r="476" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K476" s="7"/>
+    </row>
+    <row r="477" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K477" s="7"/>
+    </row>
+    <row r="478" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K478" s="7"/>
+    </row>
+    <row r="479" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K479" s="7"/>
+    </row>
+    <row r="480" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K480" s="7"/>
+    </row>
+    <row r="481" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K481" s="7"/>
+    </row>
+    <row r="482" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K482" s="7"/>
+    </row>
+    <row r="483" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K483" s="7"/>
+    </row>
+    <row r="484" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K484" s="7"/>
+    </row>
+    <row r="485" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K485" s="7"/>
+    </row>
+    <row r="486" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K486" s="7"/>
+    </row>
+    <row r="487" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K487" s="7"/>
+    </row>
+    <row r="488" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K488" s="7"/>
+    </row>
+    <row r="489" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K489" s="7"/>
+    </row>
+    <row r="490" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K490" s="7"/>
+    </row>
+    <row r="491" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K491" s="7"/>
+    </row>
+    <row r="492" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K492" s="7"/>
+    </row>
+    <row r="493" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K493" s="7"/>
+    </row>
+    <row r="494" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K494" s="7"/>
+    </row>
+    <row r="495" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K495" s="7"/>
+    </row>
+    <row r="496" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K496" s="7"/>
+    </row>
+    <row r="497" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K497" s="7"/>
+    </row>
+    <row r="498" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K498" s="7"/>
+    </row>
+    <row r="499" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K499" s="7"/>
+    </row>
+    <row r="500" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K500" s="7"/>
+    </row>
+    <row r="501" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K501" s="7"/>
+    </row>
+    <row r="502" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K502" s="7"/>
+    </row>
+    <row r="503" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K503" s="7"/>
+    </row>
+    <row r="504" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K504" s="7"/>
+    </row>
+    <row r="505" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K505" s="7"/>
+    </row>
+    <row r="506" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K506" s="7"/>
+    </row>
+    <row r="507" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K507" s="7"/>
+    </row>
+    <row r="508" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K508" s="7"/>
+    </row>
+    <row r="509" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K509" s="7"/>
+    </row>
+    <row r="510" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K510" s="7"/>
+    </row>
+    <row r="511" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K511" s="7"/>
+    </row>
+    <row r="512" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K512" s="7"/>
+    </row>
+    <row r="513" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K513" s="7"/>
+    </row>
+    <row r="514" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K514" s="7"/>
+    </row>
+    <row r="515" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K515" s="7"/>
+    </row>
+    <row r="516" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K516" s="7"/>
+    </row>
+    <row r="517" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K517" s="7"/>
+    </row>
+    <row r="518" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K518" s="7"/>
+    </row>
+    <row r="519" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K519" s="7"/>
+    </row>
+    <row r="520" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K520" s="7"/>
+    </row>
+    <row r="521" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K521" s="7"/>
+    </row>
+    <row r="522" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K522" s="7"/>
+    </row>
+    <row r="523" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K523" s="7"/>
+    </row>
+    <row r="524" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K524" s="7"/>
+    </row>
+    <row r="525" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K525" s="7"/>
+    </row>
+    <row r="526" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K526" s="7"/>
+    </row>
+    <row r="527" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K527" s="7"/>
+    </row>
+    <row r="528" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K528" s="7"/>
+    </row>
+    <row r="529" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K529" s="7"/>
+    </row>
+    <row r="530" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K530" s="7"/>
+    </row>
+    <row r="531" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K531" s="7"/>
+    </row>
+    <row r="532" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K532" s="7"/>
+    </row>
+    <row r="533" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K533" s="7"/>
+    </row>
+    <row r="534" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K534" s="7"/>
+    </row>
+    <row r="535" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K535" s="7"/>
+    </row>
+    <row r="536" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K536" s="7"/>
+    </row>
+    <row r="537" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K537" s="7"/>
+    </row>
+    <row r="538" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K538" s="7"/>
+    </row>
+    <row r="539" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K539" s="7"/>
+    </row>
+    <row r="540" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K540" s="7"/>
+    </row>
+    <row r="541" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K541" s="7"/>
+    </row>
+    <row r="542" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K542" s="7"/>
+    </row>
+    <row r="543" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K543" s="7"/>
+    </row>
+    <row r="544" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K544" s="7"/>
+    </row>
+    <row r="545" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K545" s="7"/>
+    </row>
+    <row r="546" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K546" s="7"/>
+    </row>
+    <row r="547" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K547" s="7"/>
+    </row>
+    <row r="548" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K548" s="7"/>
+    </row>
+    <row r="549" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K549" s="7"/>
+    </row>
+    <row r="550" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K550" s="7"/>
+    </row>
+    <row r="551" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K551" s="7"/>
+    </row>
+    <row r="552" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K552" s="7"/>
+    </row>
+    <row r="553" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K553" s="7"/>
+    </row>
+    <row r="554" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K554" s="7"/>
+    </row>
+    <row r="555" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K555" s="7"/>
+    </row>
+    <row r="556" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K556" s="7"/>
+    </row>
+    <row r="557" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K557" s="7"/>
+    </row>
+    <row r="558" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K558" s="7"/>
+    </row>
+    <row r="559" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K559" s="7"/>
+    </row>
+    <row r="560" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K560" s="7"/>
+    </row>
+    <row r="561" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K561" s="7"/>
+    </row>
+    <row r="562" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K562" s="7"/>
+    </row>
+    <row r="563" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K563" s="7"/>
+    </row>
+    <row r="564" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K564" s="7"/>
+    </row>
+    <row r="565" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K565" s="7"/>
+    </row>
+    <row r="566" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K566" s="7"/>
+    </row>
+    <row r="567" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K567" s="7"/>
+    </row>
+    <row r="568" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K568" s="7"/>
+    </row>
+    <row r="569" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K569" s="7"/>
+    </row>
+    <row r="570" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K570" s="7"/>
+    </row>
+    <row r="571" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K571" s="7"/>
+    </row>
+    <row r="572" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K572" s="7"/>
+    </row>
+    <row r="573" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K573" s="7"/>
+    </row>
+    <row r="574" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K574" s="7"/>
+    </row>
+    <row r="575" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K575" s="7"/>
+    </row>
+    <row r="576" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K576" s="7"/>
+    </row>
+    <row r="577" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K577" s="7"/>
+    </row>
+    <row r="578" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K578" s="7"/>
+    </row>
+    <row r="579" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K579" s="7"/>
+    </row>
+    <row r="580" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K580" s="7"/>
+    </row>
+    <row r="581" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K581" s="7"/>
+    </row>
+    <row r="582" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K582" s="7"/>
+    </row>
+    <row r="583" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K583" s="7"/>
+    </row>
+    <row r="584" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K584" s="7"/>
+    </row>
+    <row r="585" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K585" s="7"/>
+    </row>
+    <row r="586" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K586" s="7"/>
+    </row>
+    <row r="587" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K587" s="7"/>
+    </row>
+    <row r="588" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K588" s="7"/>
+    </row>
+    <row r="589" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K589" s="7"/>
+    </row>
+    <row r="590" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K590" s="7"/>
+    </row>
+    <row r="591" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K591" s="7"/>
+    </row>
+    <row r="592" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K592" s="7"/>
+    </row>
+    <row r="593" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K593" s="7"/>
+    </row>
+    <row r="594" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K594" s="7"/>
+    </row>
+    <row r="595" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K595" s="7"/>
+    </row>
+    <row r="596" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K596" s="7"/>
+    </row>
+    <row r="597" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K597" s="7"/>
+    </row>
+    <row r="598" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K598" s="7"/>
+    </row>
+    <row r="599" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K599" s="7"/>
+    </row>
+    <row r="600" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K600" s="7"/>
+    </row>
+    <row r="601" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K601" s="7"/>
+    </row>
+    <row r="602" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K602" s="7"/>
+    </row>
+    <row r="603" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K603" s="7"/>
+    </row>
+    <row r="604" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K604" s="7"/>
+    </row>
+    <row r="605" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K605" s="7"/>
+    </row>
+    <row r="606" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K606" s="7"/>
+    </row>
+    <row r="607" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K607" s="7"/>
+    </row>
+    <row r="608" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K608" s="7"/>
+    </row>
+    <row r="609" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K609" s="7"/>
+    </row>
+    <row r="610" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K610" s="7"/>
+    </row>
+    <row r="611" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K611" s="7"/>
+    </row>
+    <row r="612" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K612" s="7"/>
+    </row>
+    <row r="613" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K613" s="7"/>
+    </row>
+    <row r="614" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K614" s="7"/>
+    </row>
+    <row r="615" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K615" s="7"/>
+    </row>
+    <row r="616" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K616" s="7"/>
+    </row>
+    <row r="617" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K617" s="7"/>
+    </row>
+    <row r="618" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K618" s="7"/>
+    </row>
+    <row r="619" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K619" s="7"/>
+    </row>
+    <row r="620" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K620" s="7"/>
+    </row>
+    <row r="621" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K621" s="7"/>
+    </row>
+    <row r="622" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K622" s="7"/>
+    </row>
+    <row r="623" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K623" s="7"/>
+    </row>
+    <row r="624" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K624" s="7"/>
+    </row>
+    <row r="625" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K625" s="7"/>
+    </row>
+    <row r="626" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K626" s="7"/>
+    </row>
+    <row r="627" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K627" s="7"/>
+    </row>
+    <row r="628" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K628" s="7"/>
+    </row>
+    <row r="629" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K629" s="7"/>
+    </row>
+    <row r="630" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K630" s="7"/>
+    </row>
+    <row r="631" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K631" s="7"/>
+    </row>
+    <row r="632" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K632" s="7"/>
+    </row>
+    <row r="633" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K633" s="7"/>
+    </row>
+    <row r="634" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K634" s="7"/>
+    </row>
+    <row r="635" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K635" s="7"/>
+    </row>
+    <row r="636" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K636" s="7"/>
+    </row>
+    <row r="637" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K637" s="7"/>
+    </row>
+    <row r="638" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K638" s="7"/>
+    </row>
+    <row r="639" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K639" s="7"/>
+    </row>
+    <row r="640" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K640" s="7"/>
+    </row>
+    <row r="641" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K641" s="7"/>
+    </row>
+    <row r="642" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K642" s="7"/>
+    </row>
+    <row r="643" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K643" s="7"/>
+    </row>
+    <row r="644" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K644" s="7"/>
+    </row>
+    <row r="645" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K645" s="7"/>
+    </row>
+    <row r="646" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K646" s="7"/>
+    </row>
+    <row r="647" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K647" s="7"/>
+    </row>
+    <row r="648" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K648" s="7"/>
+    </row>
+    <row r="649" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K649" s="7"/>
+    </row>
+    <row r="650" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K650" s="7"/>
+    </row>
+    <row r="651" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K651" s="7"/>
+    </row>
+    <row r="652" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K652" s="7"/>
+    </row>
+    <row r="653" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K653" s="7"/>
+    </row>
+    <row r="654" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K654" s="7"/>
+    </row>
+    <row r="655" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K655" s="7"/>
+    </row>
+    <row r="656" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K656" s="7"/>
+    </row>
+    <row r="657" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K657" s="7"/>
+    </row>
+    <row r="658" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K658" s="7"/>
+    </row>
+    <row r="659" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K659" s="7"/>
+    </row>
+    <row r="660" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K660" s="7"/>
+    </row>
+    <row r="661" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K661" s="7"/>
+    </row>
+    <row r="662" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K662" s="7"/>
+    </row>
+    <row r="663" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K663" s="7"/>
+    </row>
+    <row r="664" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K664" s="7"/>
+    </row>
+    <row r="665" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K665" s="7"/>
+    </row>
+    <row r="666" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K666" s="7"/>
+    </row>
+    <row r="667" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K667" s="7"/>
+    </row>
+    <row r="668" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K668" s="7"/>
+    </row>
+    <row r="669" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K669" s="7"/>
+    </row>
+    <row r="670" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K670" s="7"/>
+    </row>
+    <row r="671" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K671" s="7"/>
+    </row>
+    <row r="672" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K672" s="7"/>
+    </row>
+    <row r="673" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K673" s="7"/>
+    </row>
+    <row r="674" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K674" s="7"/>
+    </row>
+    <row r="675" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K675" s="7"/>
+    </row>
+    <row r="676" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K676" s="7"/>
+    </row>
+    <row r="677" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K677" s="7"/>
+    </row>
+    <row r="678" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K678" s="7"/>
+    </row>
+    <row r="679" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K679" s="7"/>
+    </row>
+    <row r="680" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K680" s="7"/>
+    </row>
+    <row r="681" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K681" s="7"/>
+    </row>
+    <row r="682" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K682" s="7"/>
+    </row>
+    <row r="683" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K683" s="7"/>
+    </row>
+    <row r="684" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K684" s="7"/>
+    </row>
+    <row r="685" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K685" s="7"/>
+    </row>
+    <row r="686" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K686" s="7"/>
+    </row>
+    <row r="687" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K687" s="7"/>
+    </row>
+    <row r="688" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K688" s="7"/>
+    </row>
+    <row r="689" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K689" s="7"/>
+    </row>
+    <row r="690" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K690" s="7"/>
+    </row>
+    <row r="691" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K691" s="7"/>
+    </row>
+    <row r="692" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K692" s="7"/>
+    </row>
+    <row r="693" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K693" s="7"/>
+    </row>
+    <row r="694" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K694" s="7"/>
+    </row>
+    <row r="695" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K695" s="7"/>
+    </row>
+    <row r="696" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K696" s="7"/>
+    </row>
+    <row r="697" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K697" s="7"/>
+    </row>
+    <row r="698" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K698" s="7"/>
+    </row>
+    <row r="699" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K699" s="7"/>
+    </row>
+    <row r="700" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K700" s="7"/>
+    </row>
+    <row r="701" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K701" s="7"/>
+    </row>
+    <row r="702" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K702" s="7"/>
+    </row>
+    <row r="703" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K703" s="7"/>
+    </row>
+    <row r="704" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K704" s="7"/>
+    </row>
+    <row r="705" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K705" s="7"/>
+    </row>
+    <row r="706" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K706" s="7"/>
+    </row>
+    <row r="707" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K707" s="7"/>
+    </row>
+    <row r="708" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K708" s="7"/>
+    </row>
+    <row r="709" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K709" s="7"/>
+    </row>
+    <row r="710" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K710" s="7"/>
+    </row>
+    <row r="711" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K711" s="7"/>
+    </row>
+    <row r="712" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K712" s="7"/>
+    </row>
+    <row r="713" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K713" s="7"/>
+    </row>
+    <row r="714" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K714" s="7"/>
+    </row>
+    <row r="715" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K715" s="7"/>
+    </row>
+    <row r="716" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K716" s="7"/>
+    </row>
+    <row r="717" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K717" s="7"/>
+    </row>
+    <row r="718" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K718" s="7"/>
+    </row>
+    <row r="719" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K719" s="7"/>
+    </row>
+    <row r="720" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K720" s="7"/>
+    </row>
+    <row r="721" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K721" s="7"/>
+    </row>
+    <row r="722" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K722" s="7"/>
+    </row>
+    <row r="723" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K723" s="7"/>
+    </row>
+    <row r="724" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K724" s="7"/>
+    </row>
+    <row r="725" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K725" s="7"/>
+    </row>
+    <row r="726" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K726" s="7"/>
+    </row>
+    <row r="727" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K727" s="7"/>
+    </row>
+    <row r="728" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K728" s="7"/>
+    </row>
+    <row r="729" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K729" s="7"/>
+    </row>
+    <row r="730" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K730" s="7"/>
+    </row>
+    <row r="731" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K731" s="7"/>
+    </row>
+    <row r="732" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K732" s="7"/>
+    </row>
+    <row r="733" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K733" s="7"/>
+    </row>
+    <row r="734" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K734" s="7"/>
+    </row>
+    <row r="735" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K735" s="7"/>
+    </row>
+    <row r="736" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K736" s="7"/>
+    </row>
+    <row r="737" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K737" s="7"/>
+    </row>
+    <row r="738" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K738" s="7"/>
+    </row>
+    <row r="739" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K739" s="7"/>
+    </row>
+    <row r="740" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K740" s="7"/>
+    </row>
+    <row r="741" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K741" s="7"/>
+    </row>
+    <row r="742" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K742" s="7"/>
+    </row>
+    <row r="743" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K743" s="7"/>
+    </row>
+    <row r="744" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K744" s="7"/>
+    </row>
+    <row r="745" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K745" s="7"/>
+    </row>
+    <row r="746" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K746" s="7"/>
+    </row>
+    <row r="747" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K747" s="7"/>
+    </row>
+    <row r="748" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K748" s="7"/>
+    </row>
+    <row r="749" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K749" s="7"/>
+    </row>
+    <row r="750" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K750" s="7"/>
+    </row>
+    <row r="751" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K751" s="7"/>
+    </row>
+    <row r="752" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K752" s="7"/>
+    </row>
+    <row r="753" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K753" s="7"/>
+    </row>
+    <row r="754" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K754" s="7"/>
+    </row>
+    <row r="755" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K755" s="7"/>
+    </row>
+    <row r="756" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K756" s="7"/>
+    </row>
+    <row r="757" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K757" s="7"/>
+    </row>
+    <row r="758" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K758" s="7"/>
+    </row>
+    <row r="759" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K759" s="7"/>
+    </row>
+    <row r="760" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K760" s="7"/>
+    </row>
+    <row r="761" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K761" s="7"/>
+    </row>
+    <row r="762" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K762" s="7"/>
+    </row>
+    <row r="763" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K763" s="7"/>
+    </row>
+    <row r="764" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K764" s="7"/>
+    </row>
+    <row r="765" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K765" s="7"/>
+    </row>
+    <row r="766" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K766" s="7"/>
+    </row>
+    <row r="767" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K767" s="7"/>
+    </row>
+    <row r="768" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K768" s="7"/>
+    </row>
+    <row r="769" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K769" s="7"/>
+    </row>
+    <row r="770" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K770" s="7"/>
+    </row>
+    <row r="771" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K771" s="7"/>
+    </row>
+    <row r="772" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K772" s="7"/>
+    </row>
+    <row r="773" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K773" s="7"/>
+    </row>
+    <row r="774" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K774" s="7"/>
+    </row>
+    <row r="775" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K775" s="7"/>
+    </row>
+    <row r="776" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K776" s="7"/>
+    </row>
+    <row r="777" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K777" s="7"/>
+    </row>
+    <row r="778" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K778" s="7"/>
+    </row>
+    <row r="779" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K779" s="7"/>
+    </row>
+    <row r="780" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K780" s="7"/>
+    </row>
+    <row r="781" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K781" s="7"/>
+    </row>
+    <row r="782" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K782" s="7"/>
+    </row>
+    <row r="783" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K783" s="7"/>
+    </row>
+    <row r="784" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K784" s="7"/>
+    </row>
+    <row r="785" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K785" s="7"/>
+    </row>
+    <row r="786" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K786" s="7"/>
+    </row>
+    <row r="787" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K787" s="7"/>
+    </row>
+    <row r="788" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K788" s="7"/>
+    </row>
+    <row r="789" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K789" s="7"/>
+    </row>
+    <row r="790" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K790" s="7"/>
+    </row>
+    <row r="791" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K791" s="7"/>
+    </row>
+    <row r="792" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K792" s="7"/>
+    </row>
+    <row r="793" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K793" s="7"/>
+    </row>
+    <row r="794" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K794" s="7"/>
+    </row>
+    <row r="795" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K795" s="7"/>
+    </row>
+    <row r="796" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K796" s="7"/>
+    </row>
+    <row r="797" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K797" s="7"/>
+    </row>
+    <row r="798" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K798" s="7"/>
+    </row>
+    <row r="799" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K799" s="7"/>
+    </row>
+    <row r="800" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K800" s="7"/>
+    </row>
+    <row r="801" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K801" s="7"/>
+    </row>
+    <row r="802" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K802" s="7"/>
+    </row>
+    <row r="803" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K803" s="7"/>
+    </row>
+    <row r="804" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K804" s="7"/>
+    </row>
+    <row r="805" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K805" s="7"/>
+    </row>
+    <row r="806" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K806" s="7"/>
+    </row>
+    <row r="807" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K807" s="7"/>
+    </row>
+    <row r="808" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K808" s="7"/>
+    </row>
+    <row r="809" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K809" s="7"/>
+    </row>
+    <row r="810" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K810" s="7"/>
+    </row>
+    <row r="811" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K811" s="7"/>
+    </row>
+    <row r="812" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K812" s="7"/>
+    </row>
+    <row r="813" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K813" s="7"/>
+    </row>
+    <row r="814" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K814" s="7"/>
+    </row>
+    <row r="815" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K815" s="7"/>
+    </row>
+    <row r="816" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K816" s="7"/>
+    </row>
+    <row r="817" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K817" s="7"/>
+    </row>
+    <row r="818" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K818" s="7"/>
+    </row>
+    <row r="819" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K819" s="7"/>
+    </row>
+    <row r="820" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K820" s="7"/>
+    </row>
+    <row r="821" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K821" s="7"/>
+    </row>
+    <row r="822" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K822" s="7"/>
+    </row>
+    <row r="823" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K823" s="7"/>
+    </row>
+    <row r="824" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K824" s="7"/>
+    </row>
+    <row r="825" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K825" s="7"/>
+    </row>
+    <row r="826" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K826" s="7"/>
+    </row>
+    <row r="827" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K827" s="7"/>
+    </row>
+    <row r="828" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K828" s="7"/>
+    </row>
+    <row r="829" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K829" s="7"/>
+    </row>
+    <row r="830" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K830" s="7"/>
+    </row>
+    <row r="831" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K831" s="7"/>
+    </row>
+    <row r="832" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K832" s="7"/>
+    </row>
+    <row r="833" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K833" s="7"/>
+    </row>
+    <row r="834" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K834" s="7"/>
+    </row>
+    <row r="835" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K835" s="7"/>
+    </row>
+    <row r="836" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K836" s="7"/>
+    </row>
+    <row r="837" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K837" s="7"/>
+    </row>
+    <row r="838" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K838" s="7"/>
+    </row>
+    <row r="839" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K839" s="7"/>
+    </row>
+    <row r="840" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K840" s="7"/>
+    </row>
+    <row r="841" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K841" s="7"/>
+    </row>
+    <row r="842" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K842" s="7"/>
+    </row>
+    <row r="843" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K843" s="7"/>
+    </row>
+    <row r="844" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K844" s="7"/>
+    </row>
+    <row r="845" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K845" s="7"/>
+    </row>
+    <row r="846" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K846" s="7"/>
+    </row>
+    <row r="847" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K847" s="7"/>
+    </row>
+    <row r="848" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K848" s="7"/>
+    </row>
+    <row r="849" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K849" s="7"/>
+    </row>
+    <row r="850" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K850" s="7"/>
+    </row>
+    <row r="851" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K851" s="7"/>
+    </row>
+    <row r="852" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K852" s="7"/>
+    </row>
+    <row r="853" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K853" s="7"/>
+    </row>
+    <row r="854" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K854" s="7"/>
+    </row>
+    <row r="855" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K855" s="7"/>
+    </row>
+    <row r="856" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K856" s="7"/>
+    </row>
+    <row r="857" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K857" s="7"/>
+    </row>
+    <row r="858" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K858" s="7"/>
+    </row>
+    <row r="859" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K859" s="7"/>
+    </row>
+    <row r="860" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K860" s="7"/>
+    </row>
+    <row r="861" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K861" s="7"/>
+    </row>
+    <row r="862" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K862" s="7"/>
+    </row>
+    <row r="863" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K863" s="7"/>
+    </row>
+    <row r="864" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K864" s="7"/>
+    </row>
+    <row r="865" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K865" s="7"/>
+    </row>
+    <row r="866" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K866" s="7"/>
+    </row>
+    <row r="867" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K867" s="7"/>
+    </row>
+    <row r="868" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K868" s="7"/>
+    </row>
+    <row r="869" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K869" s="7"/>
+    </row>
+    <row r="870" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K870" s="7"/>
+    </row>
+    <row r="871" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K871" s="7"/>
+    </row>
+    <row r="872" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K872" s="7"/>
+    </row>
+    <row r="873" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K873" s="7"/>
+    </row>
+    <row r="874" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K874" s="7"/>
+    </row>
+    <row r="875" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K875" s="7"/>
+    </row>
+    <row r="876" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K876" s="7"/>
+    </row>
+    <row r="877" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K877" s="7"/>
+    </row>
+    <row r="878" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K878" s="7"/>
+    </row>
+    <row r="879" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K879" s="7"/>
+    </row>
+    <row r="880" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K880" s="7"/>
+    </row>
+    <row r="881" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K881" s="7"/>
+    </row>
+    <row r="882" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K882" s="7"/>
+    </row>
+    <row r="883" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K883" s="7"/>
+    </row>
+    <row r="884" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K884" s="7"/>
+    </row>
+    <row r="885" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K885" s="7"/>
+    </row>
+    <row r="886" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K886" s="7"/>
+    </row>
+    <row r="887" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K887" s="7"/>
+    </row>
+    <row r="888" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K888" s="7"/>
+    </row>
+    <row r="889" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K889" s="7"/>
+    </row>
+    <row r="890" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K890" s="7"/>
+    </row>
+    <row r="891" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K891" s="7"/>
+    </row>
+    <row r="892" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K892" s="7"/>
+    </row>
+    <row r="893" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K893" s="7"/>
+    </row>
+    <row r="894" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K894" s="7"/>
+    </row>
+    <row r="895" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K895" s="7"/>
+    </row>
+    <row r="896" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K896" s="7"/>
+    </row>
+    <row r="897" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K897" s="7"/>
+    </row>
+    <row r="898" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K898" s="7"/>
+    </row>
+    <row r="899" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K899" s="7"/>
+    </row>
+    <row r="900" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K900" s="7"/>
+    </row>
+    <row r="901" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K901" s="7"/>
+    </row>
+    <row r="902" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K902" s="7"/>
+    </row>
+    <row r="903" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K903" s="7"/>
+    </row>
+    <row r="904" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K904" s="7"/>
+    </row>
+    <row r="905" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K905" s="7"/>
+    </row>
+    <row r="906" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K906" s="7"/>
+    </row>
+    <row r="907" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K907" s="7"/>
+    </row>
+    <row r="908" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K908" s="7"/>
+    </row>
+    <row r="909" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K909" s="7"/>
+    </row>
+    <row r="910" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K910" s="7"/>
+    </row>
+    <row r="911" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K911" s="7"/>
+    </row>
+    <row r="912" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K912" s="7"/>
+    </row>
+    <row r="913" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K913" s="7"/>
+    </row>
+    <row r="914" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K914" s="7"/>
+    </row>
+    <row r="915" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K915" s="7"/>
+    </row>
+    <row r="916" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K916" s="7"/>
+    </row>
+    <row r="917" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K917" s="7"/>
+    </row>
+    <row r="918" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K918" s="7"/>
+    </row>
+    <row r="919" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K919" s="7"/>
+    </row>
+    <row r="920" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K920" s="7"/>
+    </row>
+    <row r="921" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K921" s="7"/>
+    </row>
+    <row r="922" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K922" s="7"/>
+    </row>
+    <row r="923" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K923" s="7"/>
+    </row>
+    <row r="924" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K924" s="7"/>
+    </row>
+    <row r="925" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K925" s="7"/>
+    </row>
+    <row r="926" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K926" s="7"/>
+    </row>
+    <row r="927" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K927" s="7"/>
+    </row>
+    <row r="928" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K928" s="7"/>
+    </row>
+    <row r="929" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K929" s="7"/>
+    </row>
+    <row r="930" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K930" s="7"/>
+    </row>
+    <row r="931" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K931" s="7"/>
+    </row>
+    <row r="932" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K932" s="7"/>
+    </row>
+    <row r="933" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K933" s="7"/>
+    </row>
+    <row r="934" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K934" s="7"/>
+    </row>
+    <row r="935" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K935" s="7"/>
+    </row>
+    <row r="936" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K936" s="7"/>
+    </row>
+    <row r="937" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K937" s="7"/>
+    </row>
+    <row r="938" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K938" s="7"/>
+    </row>
+    <row r="939" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K939" s="7"/>
+    </row>
+    <row r="940" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K940" s="7"/>
+    </row>
+    <row r="941" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K941" s="7"/>
+    </row>
+    <row r="942" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K942" s="7"/>
+    </row>
+    <row r="943" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K943" s="7"/>
+    </row>
+    <row r="944" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K944" s="7"/>
+    </row>
+    <row r="945" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K945" s="7"/>
+    </row>
+    <row r="946" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K946" s="7"/>
+    </row>
+    <row r="947" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K947" s="7"/>
+    </row>
+    <row r="948" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K948" s="7"/>
+    </row>
+    <row r="949" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K949" s="7"/>
+    </row>
+    <row r="950" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K950" s="7"/>
+    </row>
+    <row r="951" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K951" s="7"/>
+    </row>
+    <row r="952" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K952" s="7"/>
+    </row>
+    <row r="953" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K953" s="7"/>
+    </row>
+    <row r="954" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K954" s="7"/>
+    </row>
+    <row r="955" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K955" s="7"/>
+    </row>
+    <row r="956" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K956" s="7"/>
+    </row>
+    <row r="957" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K957" s="7"/>
+    </row>
+    <row r="958" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K958" s="7"/>
+    </row>
+    <row r="959" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K959" s="7"/>
+    </row>
+    <row r="960" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K960" s="7"/>
+    </row>
+    <row r="961" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K961" s="7"/>
+    </row>
+    <row r="962" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K962" s="7"/>
+    </row>
+    <row r="963" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K963" s="7"/>
+    </row>
+    <row r="964" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K964" s="7"/>
+    </row>
+    <row r="965" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K965" s="7"/>
+    </row>
+    <row r="966" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K966" s="7"/>
+    </row>
+    <row r="967" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K967" s="7"/>
+    </row>
+    <row r="968" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K968" s="7"/>
+    </row>
+    <row r="969" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K969" s="7"/>
+    </row>
+    <row r="970" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K970" s="7"/>
+    </row>
+    <row r="971" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K971" s="7"/>
+    </row>
+    <row r="972" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K972" s="7"/>
+    </row>
+    <row r="973" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K973" s="7"/>
+    </row>
+    <row r="974" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K974" s="7"/>
+    </row>
+    <row r="975" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K975" s="7"/>
+    </row>
+    <row r="976" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K976" s="7"/>
+    </row>
+    <row r="977" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K977" s="7"/>
+    </row>
+    <row r="978" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K978" s="7"/>
+    </row>
+    <row r="979" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K979" s="7"/>
+    </row>
+    <row r="980" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K980" s="7"/>
+    </row>
+    <row r="981" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K981" s="7"/>
+    </row>
+    <row r="982" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K982" s="7"/>
+    </row>
+    <row r="983" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K983" s="7"/>
+    </row>
+    <row r="984" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K984" s="7"/>
+    </row>
+    <row r="985" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K985" s="7"/>
+    </row>
+    <row r="986" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K986" s="7"/>
+    </row>
+    <row r="987" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K987" s="7"/>
+    </row>
+    <row r="988" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K988" s="7"/>
+    </row>
+    <row r="989" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K989" s="7"/>
+    </row>
+    <row r="990" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K990" s="7"/>
+    </row>
+    <row r="991" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K991" s="7"/>
+    </row>
+    <row r="992" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K992" s="7"/>
+    </row>
+    <row r="993" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K993" s="7"/>
+    </row>
+    <row r="994" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K994" s="7"/>
+    </row>
+    <row r="995" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K995" s="7"/>
+    </row>
+    <row r="996" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K996" s="7"/>
+    </row>
+    <row r="997" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K997" s="7"/>
+    </row>
+    <row r="998" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K998" s="7"/>
+    </row>
+    <row r="999" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K999" s="7"/>
+    </row>
+    <row r="1000" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1000" s="7"/>
+    </row>
+    <row r="1001" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1001" s="7"/>
+    </row>
+    <row r="1002" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1002" s="7"/>
+    </row>
+    <row r="1003" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1003" s="7"/>
+    </row>
+    <row r="1004" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1004" s="7"/>
+    </row>
+    <row r="1005" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1005" s="7"/>
+    </row>
+    <row r="1006" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1006" s="7"/>
+    </row>
+    <row r="1007" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1007" s="7"/>
+    </row>
+    <row r="1008" spans="11:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1008" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4">
